--- a/data/processed/criteria_matrix.xlsx
+++ b/data/processed/criteria_matrix.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K141"/>
+  <dimension ref="A1:R141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,6 +472,41 @@
           <t>p_access_road</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>C1_hasar_risk_norm</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>C1_hasar_risk_amp</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>C2_lojistik_norm</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>C2_lojistik_amp</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>C3_bosluk_amp</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>C4_barinma_norm</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>C4_barinma_amp</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -482,7 +517,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ABDURRAHMANGAZİ</t>
+          <t>ABDURRAHMANGAZI</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -492,22 +527,43 @@
         <v>29.25648757553958</v>
       </c>
       <c r="F2" t="n">
-        <v>15.3764705882353</v>
+        <v>34.5</v>
       </c>
       <c r="G2" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="H2" t="n">
         <v>167.0715568186552</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09662015365848554</v>
+        <v>0.09662</v>
       </c>
       <c r="J2" t="n">
-        <v>978.5294117647059</v>
+        <v>1763</v>
       </c>
       <c r="K2" t="n">
         <v>0.7387143036452418</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.009335</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -519,7 +575,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ABDURRAHMANGAZİ</t>
+          <t>ABDURRAHMANGAZI</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -529,22 +585,43 @@
         <v>29.2513590942327</v>
       </c>
       <c r="F3" t="n">
-        <v>15.3764705882353</v>
+        <v>34.5</v>
       </c>
       <c r="G3" t="n">
-        <v>0.75</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="H3" t="n">
         <v>1093.217262691544</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6322250292909919</v>
+        <v>0.632225</v>
       </c>
       <c r="J3" t="n">
-        <v>978.5294117647059</v>
+        <v>1763</v>
       </c>
       <c r="K3" t="n">
         <v>0.7069653809361209</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.399708</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -556,7 +633,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ABDURRAHMANGAZİ</t>
+          <t>ABDURRAHMANGAZI</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -566,22 +643,43 @@
         <v>29.25999121604885</v>
       </c>
       <c r="F4" t="n">
-        <v>15.3764705882353</v>
+        <v>34.5</v>
       </c>
       <c r="G4" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="H4" t="n">
         <v>456.5767270301306</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2640456242975154</v>
+        <v>0.264046</v>
       </c>
       <c r="J4" t="n">
-        <v>978.5294117647059</v>
+        <v>1763</v>
       </c>
       <c r="K4" t="n">
         <v>0.7462630228997148</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.06972</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -593,7 +691,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ABDURRAHMANGAZİ</t>
+          <t>ABDURRAHMANGAZI</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -603,22 +701,43 @@
         <v>29.26242101741815</v>
       </c>
       <c r="F5" t="n">
-        <v>15.3764705882353</v>
+        <v>34.5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.75</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="H5" t="n">
         <v>605.9032860942979</v>
       </c>
       <c r="I5" t="n">
-        <v>0.350403561919018</v>
+        <v>0.350404</v>
       </c>
       <c r="J5" t="n">
-        <v>978.5294117647059</v>
+        <v>1763</v>
       </c>
       <c r="K5" t="n">
         <v>0.7900300888150814</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.122783</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -630,7 +749,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ABDURRAHMANGAZİ</t>
+          <t>ABDURRAHMANGAZI</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -640,7 +759,7 @@
         <v>29.25452742625226</v>
       </c>
       <c r="F6" t="n">
-        <v>15.3764705882353</v>
+        <v>34.5</v>
       </c>
       <c r="G6" t="n">
         <v>0.5</v>
@@ -649,13 +768,34 @@
         <v>873.7326572938648</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5052935712797748</v>
+        <v>0.505294</v>
       </c>
       <c r="J6" t="n">
-        <v>978.5294117647059</v>
+        <v>1763</v>
       </c>
       <c r="K6" t="n">
         <v>0.7021709272585134</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.255322</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -667,7 +807,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ABDURRAHMANGAZİ</t>
+          <t>ABDURRAHMANGAZI</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -677,7 +817,7 @@
         <v>29.25368362535671</v>
       </c>
       <c r="F7" t="n">
-        <v>15.3764705882353</v>
+        <v>34.5</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -686,13 +826,34 @@
         <v>488.6258586917302</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2825801497710879</v>
+        <v>0.28258</v>
       </c>
       <c r="J7" t="n">
-        <v>978.5294117647059</v>
+        <v>1763</v>
       </c>
       <c r="K7" t="n">
         <v>0.7021717481472212</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.07985200000000001</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -704,7 +865,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ABDURRAHMANGAZİ</t>
+          <t>ABDURRAHMANGAZI</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -714,22 +875,43 @@
         <v>29.25703415059688</v>
       </c>
       <c r="F8" t="n">
-        <v>15.3764705882353</v>
+        <v>34.5</v>
       </c>
       <c r="G8" t="n">
-        <v>0.75</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="H8" t="n">
         <v>561.2096104400233</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3245564944019196</v>
+        <v>0.324556</v>
       </c>
       <c r="J8" t="n">
-        <v>978.5294117647059</v>
+        <v>1763</v>
       </c>
       <c r="K8" t="n">
         <v>0.7928392367700497</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.105337</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -741,7 +923,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ADİL</t>
+          <t>ADIL</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -751,22 +933,43 @@
         <v>29.25958684878389</v>
       </c>
       <c r="F9" t="n">
-        <v>15.3764705882353</v>
+        <v>3.4</v>
       </c>
       <c r="G9" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="H9" t="n">
         <v>881.8635997799144</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5099958253758634</v>
+        <v>0.509996</v>
       </c>
       <c r="J9" t="n">
-        <v>978.5294117647059</v>
+        <v>578</v>
       </c>
       <c r="K9" t="n">
         <v>0.8893784101140766</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.260096</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -778,7 +981,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ADİL</t>
+          <t>ADIL</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -788,7 +991,7 @@
         <v>29.25752940799835</v>
       </c>
       <c r="F10" t="n">
-        <v>15.3764705882353</v>
+        <v>3.4</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -797,13 +1000,34 @@
         <v>587.0491701944831</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3394999251179776</v>
+        <v>0.3395</v>
       </c>
       <c r="J10" t="n">
-        <v>978.5294117647059</v>
+        <v>578</v>
       </c>
       <c r="K10" t="n">
         <v>0.8275329543596835</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.11526</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -815,7 +1039,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ADİL</t>
+          <t>ADIL</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -825,7 +1049,7 @@
         <v>29.25908831050796</v>
       </c>
       <c r="F11" t="n">
-        <v>15.3764705882353</v>
+        <v>3.4</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -834,13 +1058,34 @@
         <v>860.8355345898824</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4978349589274418</v>
+        <v>0.497835</v>
       </c>
       <c r="J11" t="n">
-        <v>978.5294117647059</v>
+        <v>578</v>
       </c>
       <c r="K11" t="n">
         <v>0.8781346758357294</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.24784</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -852,7 +1097,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ADİL</t>
+          <t>ADIL</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -862,22 +1107,43 @@
         <v>29.2589115278746</v>
       </c>
       <c r="F12" t="n">
-        <v>15.3764705882353</v>
+        <v>3.4</v>
       </c>
       <c r="G12" t="n">
-        <v>0.75</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="H12" t="n">
         <v>1109.691090545845</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6417521074420246</v>
+        <v>0.641752</v>
       </c>
       <c r="J12" t="n">
-        <v>978.5294117647059</v>
+        <v>578</v>
       </c>
       <c r="K12" t="n">
         <v>0.827835789015808</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.411846</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -889,7 +1155,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ADİL</t>
+          <t>ADIL</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -899,7 +1165,7 @@
         <v>29.25873569721979</v>
       </c>
       <c r="F13" t="n">
-        <v>15.3764705882353</v>
+        <v>3.4</v>
       </c>
       <c r="G13" t="n">
         <v>0.5</v>
@@ -908,13 +1174,34 @@
         <v>1142.932049859819</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6609758859105392</v>
+        <v>0.660976</v>
       </c>
       <c r="J13" t="n">
-        <v>978.5294117647059</v>
+        <v>578</v>
       </c>
       <c r="K13" t="n">
         <v>0.8277201859779183</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.436889</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -926,7 +1213,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ADİL</t>
+          <t>ADIL</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -936,22 +1223,43 @@
         <v>29.25687819743897</v>
       </c>
       <c r="F14" t="n">
-        <v>15.3764705882353</v>
+        <v>3.4</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="H14" t="n">
         <v>1273.219180636263</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7363230176129572</v>
+        <v>0.7363229999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>978.5294117647059</v>
+        <v>578</v>
       </c>
       <c r="K14" t="n">
         <v>0.8631047872347328</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.542172</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -963,7 +1271,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ADİL</t>
+          <t>ADIL</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -973,22 +1281,43 @@
         <v>29.25557463742678</v>
       </c>
       <c r="F15" t="n">
-        <v>15.3764705882353</v>
+        <v>3.4</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="H15" t="n">
         <v>1251.73249294428</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7238969224358786</v>
+        <v>0.723897</v>
       </c>
       <c r="J15" t="n">
-        <v>978.5294117647059</v>
+        <v>578</v>
       </c>
       <c r="K15" t="n">
         <v>0.7553426614235412</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.524027</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1000,7 +1329,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ADİL</t>
+          <t>ADIL</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1010,22 +1339,43 @@
         <v>29.25520144542262</v>
       </c>
       <c r="F16" t="n">
-        <v>15.3764705882353</v>
+        <v>3.4</v>
       </c>
       <c r="G16" t="n">
-        <v>0.75</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="H16" t="n">
         <v>996.0730321409661</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5760449669179567</v>
+        <v>0.576045</v>
       </c>
       <c r="J16" t="n">
-        <v>978.5294117647059</v>
+        <v>578</v>
       </c>
       <c r="K16" t="n">
         <v>0.7647607820307795</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.331828</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1037,7 +1387,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ADİL</t>
+          <t>ADIL</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1047,22 +1397,43 @@
         <v>29.26238410907338</v>
       </c>
       <c r="F17" t="n">
-        <v>15.3764705882353</v>
+        <v>3.4</v>
       </c>
       <c r="G17" t="n">
-        <v>0.75</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="H17" t="n">
         <v>1261.008303589103</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7292612721006306</v>
+        <v>0.729261</v>
       </c>
       <c r="J17" t="n">
-        <v>978.5294117647059</v>
+        <v>578</v>
       </c>
       <c r="K17" t="n">
         <v>0.8228922971943825</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.531822</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1074,7 +1445,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AHMET YESEVİ</t>
+          <t>AHMET YESEVI</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1084,7 +1455,7 @@
         <v>29.28157466186555</v>
       </c>
       <c r="F18" t="n">
-        <v>15.3764705882353</v>
+        <v>19.8</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1093,13 +1464,34 @@
         <v>941.2044340568173</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5443135790092987</v>
+        <v>0.544314</v>
       </c>
       <c r="J18" t="n">
-        <v>978.5294117647059</v>
+        <v>1305</v>
       </c>
       <c r="K18" t="n">
         <v>0.7477685198617064</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.527331</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.278078</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.296277</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.613502</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.376385</v>
       </c>
     </row>
     <row r="19">
@@ -1111,7 +1503,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AHMET YESEVİ</t>
+          <t>AHMET YESEVI</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1121,7 +1513,7 @@
         <v>29.264825621528</v>
       </c>
       <c r="F19" t="n">
-        <v>15.3764705882353</v>
+        <v>19.8</v>
       </c>
       <c r="G19" t="n">
         <v>0.5</v>
@@ -1130,13 +1522,34 @@
         <v>538.2076081238445</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3112540685398421</v>
+        <v>0.311254</v>
       </c>
       <c r="J19" t="n">
-        <v>978.5294117647059</v>
+        <v>1305</v>
       </c>
       <c r="K19" t="n">
         <v>0.8141224425081913</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.527331</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.278078</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.09687900000000001</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.613502</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.376385</v>
       </c>
     </row>
     <row r="20">
@@ -1148,7 +1561,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AHMET YESEVİ</t>
+          <t>AHMET YESEVI</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1158,22 +1571,43 @@
         <v>29.27697589832328</v>
       </c>
       <c r="F20" t="n">
-        <v>15.3764705882353</v>
+        <v>19.8</v>
       </c>
       <c r="G20" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="H20" t="n">
         <v>886.7719188378383</v>
       </c>
       <c r="I20" t="n">
-        <v>0.51283438479682</v>
+        <v>0.512834</v>
       </c>
       <c r="J20" t="n">
-        <v>978.5294117647059</v>
+        <v>1305</v>
       </c>
       <c r="K20" t="n">
         <v>0.7530088721023671</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.527331</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.278078</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.262999</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.613502</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.376385</v>
       </c>
     </row>
     <row r="21">
@@ -1185,7 +1619,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AHMET YESEVİ</t>
+          <t>AHMET YESEVI</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1195,22 +1629,43 @@
         <v>29.28119466982549</v>
       </c>
       <c r="F21" t="n">
-        <v>15.3764705882353</v>
+        <v>19.8</v>
       </c>
       <c r="G21" t="n">
-        <v>0.75</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="H21" t="n">
         <v>1052.850770240295</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6088804410345532</v>
+        <v>0.60888</v>
       </c>
       <c r="J21" t="n">
-        <v>978.5294117647059</v>
+        <v>1305</v>
       </c>
       <c r="K21" t="n">
         <v>0.727794890811663</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.527331</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.278078</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.370735</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.613502</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.376385</v>
       </c>
     </row>
     <row r="22">
@@ -1222,7 +1677,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AHMET YESEVİ</t>
+          <t>AHMET YESEVI</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1232,7 +1687,7 @@
         <v>29.27403441655196</v>
       </c>
       <c r="F22" t="n">
-        <v>15.3764705882353</v>
+        <v>19.8</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1241,13 +1696,34 @@
         <v>704.3786116136109</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4073534178036614</v>
+        <v>0.407353</v>
       </c>
       <c r="J22" t="n">
-        <v>978.5294117647059</v>
+        <v>1305</v>
       </c>
       <c r="K22" t="n">
         <v>0.8716925143245053</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.527331</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.278078</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.165937</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.613502</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.376385</v>
       </c>
     </row>
     <row r="23">
@@ -1259,7 +1735,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AHMET YESEVİ</t>
+          <t>AHMET YESEVI</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1269,22 +1745,43 @@
         <v>29.27517770913529</v>
       </c>
       <c r="F23" t="n">
-        <v>15.3764705882353</v>
+        <v>19.8</v>
       </c>
       <c r="G23" t="n">
-        <v>0.75</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="H23" t="n">
         <v>883.1374528899897</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5107325150050108</v>
+        <v>0.510733</v>
       </c>
       <c r="J23" t="n">
-        <v>978.5294117647059</v>
+        <v>1305</v>
       </c>
       <c r="K23" t="n">
         <v>0.7871212608541008</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.527331</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.278078</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.260848</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.613502</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.376385</v>
       </c>
     </row>
     <row r="24">
@@ -1296,7 +1793,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AHMET YESEVİ</t>
+          <t>AHMET YESEVI</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1306,7 +1803,7 @@
         <v>29.27360187332038</v>
       </c>
       <c r="F24" t="n">
-        <v>15.3764705882353</v>
+        <v>19.8</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1315,13 +1812,34 @@
         <v>780.135576873587</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4511648825646225</v>
+        <v>0.451165</v>
       </c>
       <c r="J24" t="n">
-        <v>978.5294117647059</v>
+        <v>1305</v>
       </c>
       <c r="K24" t="n">
         <v>0.8017864861128238</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.527331</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.278078</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.20355</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.613502</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.376385</v>
       </c>
     </row>
     <row r="25">
@@ -1333,7 +1851,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AHMET YESEVİ</t>
+          <t>AHMET YESEVI</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1343,22 +1861,43 @@
         <v>29.26542748570276</v>
       </c>
       <c r="F25" t="n">
-        <v>15.3764705882353</v>
+        <v>19.8</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="H25" t="n">
         <v>368.3820710225573</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2130412440333248</v>
+        <v>0.213041</v>
       </c>
       <c r="J25" t="n">
-        <v>978.5294117647059</v>
+        <v>1305</v>
       </c>
       <c r="K25" t="n">
         <v>0.7271726665677548</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.527331</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.278078</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.045387</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.613502</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.376385</v>
       </c>
     </row>
     <row r="26">
@@ -1370,7 +1909,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AHMET YESEVİ</t>
+          <t>AHMET YESEVI</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1380,22 +1919,43 @@
         <v>29.26604512019534</v>
       </c>
       <c r="F26" t="n">
-        <v>15.3764705882353</v>
+        <v>19.8</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="H26" t="n">
         <v>331.1167262517001</v>
       </c>
       <c r="I26" t="n">
-        <v>0.191490099084069</v>
+        <v>0.19149</v>
       </c>
       <c r="J26" t="n">
-        <v>978.5294117647059</v>
+        <v>1305</v>
       </c>
       <c r="K26" t="n">
         <v>0.7711909396521685</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.527331</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.278078</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.036668</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.613502</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.376385</v>
       </c>
     </row>
     <row r="27">
@@ -1407,7 +1967,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AKŞEMSETTİN</t>
+          <t>AKSEMSETTIN</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1417,10 +1977,10 @@
         <v>29.30228786317313</v>
       </c>
       <c r="F27" t="n">
-        <v>15.3764705882353</v>
+        <v>8.9</v>
       </c>
       <c r="G27" t="n">
-        <v>0.75</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1429,10 +1989,31 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>978.5294117647059</v>
+        <v>631</v>
       </c>
       <c r="K27" t="n">
         <v>0.6027291250038129</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.176849</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.031276</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.044726</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.002</v>
       </c>
     </row>
     <row r="28">
@@ -1444,7 +2025,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AKŞEMSETTİN</t>
+          <t>AKSEMSETTIN</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1454,22 +2035,43 @@
         <v>29.30469129403843</v>
       </c>
       <c r="F28" t="n">
-        <v>15.3764705882353</v>
+        <v>8.9</v>
       </c>
       <c r="G28" t="n">
-        <v>0.75</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="H28" t="n">
         <v>229.4180073293889</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1326761032355091</v>
+        <v>0.132676</v>
       </c>
       <c r="J28" t="n">
-        <v>978.5294117647059</v>
+        <v>631</v>
       </c>
       <c r="K28" t="n">
         <v>0.5396333166472045</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.176849</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.031276</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.017603</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.044726</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.002</v>
       </c>
     </row>
     <row r="29">
@@ -1481,7 +2083,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AKŞEMSETTİN</t>
+          <t>AKSEMSETTIN</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1491,22 +2093,43 @@
         <v>29.29711942047134</v>
       </c>
       <c r="F29" t="n">
-        <v>15.3764705882353</v>
+        <v>8.9</v>
       </c>
       <c r="G29" t="n">
-        <v>0.75</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="H29" t="n">
         <v>521.8545708073576</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3017968454889015</v>
+        <v>0.301797</v>
       </c>
       <c r="J29" t="n">
-        <v>978.5294117647059</v>
+        <v>631</v>
       </c>
       <c r="K29" t="n">
         <v>0.6159678964356032</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.176849</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.031276</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.091081</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.044726</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.002</v>
       </c>
     </row>
     <row r="30">
@@ -1518,7 +2141,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AKŞEMSETTİN</t>
+          <t>AKSEMSETTIN</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1528,22 +2151,43 @@
         <v>29.30035388398099</v>
       </c>
       <c r="F30" t="n">
-        <v>15.3764705882353</v>
+        <v>8.9</v>
       </c>
       <c r="G30" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="H30" t="n">
         <v>614.1954813320059</v>
       </c>
       <c r="I30" t="n">
-        <v>0.3551990710606677</v>
+        <v>0.355199</v>
       </c>
       <c r="J30" t="n">
-        <v>978.5294117647059</v>
+        <v>631</v>
       </c>
       <c r="K30" t="n">
         <v>0.5671510610223794</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.176849</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.031276</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.126166</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.044726</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.002</v>
       </c>
     </row>
     <row r="31">
@@ -1555,7 +2199,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AKŞEMSETTİN</t>
+          <t>AKSEMSETTIN</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1565,22 +2209,43 @@
         <v>29.29872570873468</v>
       </c>
       <c r="F31" t="n">
-        <v>15.3764705882353</v>
+        <v>8.9</v>
       </c>
       <c r="G31" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="H31" t="n">
         <v>338.3199015027646</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1956558105483028</v>
+        <v>0.195656</v>
       </c>
       <c r="J31" t="n">
-        <v>978.5294117647059</v>
+        <v>631</v>
       </c>
       <c r="K31" t="n">
         <v>0.5825983080286559</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.176849</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.031276</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.038281</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.044726</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.002</v>
       </c>
     </row>
     <row r="32">
@@ -1592,7 +2257,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AKŞEMSETTİN</t>
+          <t>AKSEMSETTIN</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1602,7 +2267,7 @@
         <v>29.30190211038684</v>
       </c>
       <c r="F32" t="n">
-        <v>15.3764705882353</v>
+        <v>8.9</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1611,13 +2276,34 @@
         <v>134.6887452701878</v>
       </c>
       <c r="I32" t="n">
-        <v>0.07789265576904626</v>
+        <v>0.077893</v>
       </c>
       <c r="J32" t="n">
-        <v>978.5294117647059</v>
+        <v>631</v>
       </c>
       <c r="K32" t="n">
         <v>0.5670976649068498</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.176849</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.031276</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.006067</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.044726</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.002</v>
       </c>
     </row>
     <row r="33">
@@ -1629,7 +2315,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1639,22 +2325,43 @@
         <v>29.28416930058134</v>
       </c>
       <c r="F33" t="n">
-        <v>15.3764705882353</v>
+        <v>18.4</v>
       </c>
       <c r="G33" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="H33" t="n">
         <v>213.1765861575888</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1232834295863683</v>
+        <v>0.123283</v>
       </c>
       <c r="J33" t="n">
-        <v>978.5294117647059</v>
+        <v>1470</v>
       </c>
       <c r="K33" t="n">
         <v>0.9707570881098774</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.482315</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.232628</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.015199</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.7527430000000001</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.566621</v>
       </c>
     </row>
     <row r="34">
@@ -1666,7 +2373,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1676,7 +2383,7 @@
         <v>29.28224476904101</v>
       </c>
       <c r="F34" t="n">
-        <v>15.3764705882353</v>
+        <v>18.4</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1685,13 +2392,34 @@
         <v>487.5154057575033</v>
       </c>
       <c r="I34" t="n">
-        <v>0.2819379570772593</v>
+        <v>0.281938</v>
       </c>
       <c r="J34" t="n">
-        <v>978.5294117647059</v>
+        <v>1470</v>
       </c>
       <c r="K34" t="n">
         <v>0.8774683176475337</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.482315</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.232628</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.079489</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.7527430000000001</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0.566621</v>
       </c>
     </row>
     <row r="35">
@@ -1703,7 +2431,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1713,22 +2441,43 @@
         <v>29.27937574047541</v>
       </c>
       <c r="F35" t="n">
-        <v>15.3764705882353</v>
+        <v>18.4</v>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="H35" t="n">
         <v>521.7477143473409</v>
       </c>
       <c r="I35" t="n">
-        <v>0.3017350486888787</v>
+        <v>0.301735</v>
       </c>
       <c r="J35" t="n">
-        <v>978.5294117647059</v>
+        <v>1470</v>
       </c>
       <c r="K35" t="n">
         <v>0.8252576324366355</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.482315</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.232628</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.091044</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.7527430000000001</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.566621</v>
       </c>
     </row>
     <row r="36">
@@ -1740,7 +2489,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1750,22 +2499,43 @@
         <v>29.26839981314643</v>
       </c>
       <c r="F36" t="n">
-        <v>15.3764705882353</v>
+        <v>18.4</v>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="H36" t="n">
         <v>975.8961985902598</v>
       </c>
       <c r="I36" t="n">
-        <v>0.5643763813422146</v>
+        <v>0.564376</v>
       </c>
       <c r="J36" t="n">
-        <v>978.5294117647059</v>
+        <v>1470</v>
       </c>
       <c r="K36" t="n">
         <v>0.91927042448959</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.482315</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.232628</v>
+      </c>
+      <c r="N36" t="n">
+        <v>1</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.318521</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.7527430000000001</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.566621</v>
       </c>
     </row>
     <row r="37">
@@ -1777,7 +2547,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1787,22 +2557,43 @@
         <v>29.26898331790146</v>
       </c>
       <c r="F37" t="n">
-        <v>15.3764705882353</v>
+        <v>18.4</v>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="H37" t="n">
         <v>827.2259942654506</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4783980241650367</v>
+        <v>0.478398</v>
       </c>
       <c r="J37" t="n">
-        <v>978.5294117647059</v>
+        <v>1470</v>
       </c>
       <c r="K37" t="n">
         <v>0.8171009963858794</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.482315</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.232628</v>
+      </c>
+      <c r="N37" t="n">
+        <v>1</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.228865</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.7527430000000001</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.566621</v>
       </c>
     </row>
     <row r="38">
@@ -1814,7 +2605,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1824,7 +2615,7 @@
         <v>29.26470425297333</v>
       </c>
       <c r="F38" t="n">
-        <v>15.3764705882353</v>
+        <v>18.4</v>
       </c>
       <c r="G38" t="n">
         <v>0.5</v>
@@ -1833,13 +2624,34 @@
         <v>573.9199981206863</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3319071149033948</v>
+        <v>0.331907</v>
       </c>
       <c r="J38" t="n">
-        <v>978.5294117647059</v>
+        <v>1470</v>
       </c>
       <c r="K38" t="n">
         <v>0.8885863586346683</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.482315</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.232628</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.110162</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0.7527430000000001</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.566621</v>
       </c>
     </row>
     <row r="39">
@@ -1851,7 +2663,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1861,22 +2673,43 @@
         <v>29.27908383914329</v>
       </c>
       <c r="F39" t="n">
-        <v>15.3764705882353</v>
+        <v>18.4</v>
       </c>
       <c r="G39" t="n">
-        <v>0.75</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="H39" t="n">
         <v>780.1200020986857</v>
       </c>
       <c r="I39" t="n">
-        <v>0.4511558754231748</v>
+        <v>0.451156</v>
       </c>
       <c r="J39" t="n">
-        <v>978.5294117647059</v>
+        <v>1470</v>
       </c>
       <c r="K39" t="n">
         <v>0.7801596726904417</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.482315</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.232628</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.203542</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0.7527430000000001</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0.566621</v>
       </c>
     </row>
     <row r="40">
@@ -1888,7 +2721,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1898,22 +2731,43 @@
         <v>29.278957941825</v>
       </c>
       <c r="F40" t="n">
-        <v>15.3764705882353</v>
+        <v>18.4</v>
       </c>
       <c r="G40" t="n">
-        <v>0.75</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="H40" t="n">
         <v>629.5949130104329</v>
       </c>
       <c r="I40" t="n">
-        <v>0.3641048087179637</v>
+        <v>0.364105</v>
       </c>
       <c r="J40" t="n">
-        <v>978.5294117647059</v>
+        <v>1470</v>
       </c>
       <c r="K40" t="n">
         <v>0.811733876439509</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.482315</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.232628</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.132572</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.7527430000000001</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0.566621</v>
       </c>
     </row>
     <row r="41">
@@ -1925,7 +2779,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1935,22 +2789,43 @@
         <v>29.28393190943841</v>
       </c>
       <c r="F41" t="n">
-        <v>15.3764705882353</v>
+        <v>18.4</v>
       </c>
       <c r="G41" t="n">
-        <v>0.75</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="H41" t="n">
         <v>224.3063063438721</v>
       </c>
       <c r="I41" t="n">
-        <v>0.129719924792682</v>
+        <v>0.12972</v>
       </c>
       <c r="J41" t="n">
-        <v>978.5294117647059</v>
+        <v>1470</v>
       </c>
       <c r="K41" t="n">
         <v>0.8879862406778867</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.482315</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.232628</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0.016827</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0.7527430000000001</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0.566621</v>
       </c>
     </row>
     <row r="42">
@@ -1962,7 +2837,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1972,7 +2847,7 @@
         <v>29.26573306296866</v>
       </c>
       <c r="F42" t="n">
-        <v>15.3764705882353</v>
+        <v>18.4</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1981,13 +2856,34 @@
         <v>813.8933331830804</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4706875330019396</v>
+        <v>0.470688</v>
       </c>
       <c r="J42" t="n">
-        <v>978.5294117647059</v>
+        <v>1470</v>
       </c>
       <c r="K42" t="n">
         <v>0.9150665078842011</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.482315</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.232628</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0.221547</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0.7527430000000001</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0.566621</v>
       </c>
     </row>
     <row r="43">
@@ -1999,7 +2895,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -2009,22 +2905,43 @@
         <v>29.27005014068656</v>
       </c>
       <c r="F43" t="n">
-        <v>15.3764705882353</v>
+        <v>18.4</v>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="H43" t="n">
         <v>933.4323976207152</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5398188860226844</v>
+        <v>0.539819</v>
       </c>
       <c r="J43" t="n">
-        <v>978.5294117647059</v>
+        <v>1470</v>
       </c>
       <c r="K43" t="n">
         <v>0.886711592943929</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.482315</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.232628</v>
+      </c>
+      <c r="N43" t="n">
+        <v>1</v>
+      </c>
+      <c r="O43" t="n">
+        <v>1</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0.291404</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0.7527430000000001</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0.566621</v>
       </c>
     </row>
     <row r="44">
@@ -2036,7 +2953,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -2046,22 +2963,43 @@
         <v>29.27066944344426</v>
       </c>
       <c r="F44" t="n">
-        <v>15.3764705882353</v>
+        <v>18.4</v>
       </c>
       <c r="G44" t="n">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="H44" t="n">
         <v>917.3808097152449</v>
       </c>
       <c r="I44" t="n">
-        <v>0.5305359959878916</v>
+        <v>0.530536</v>
       </c>
       <c r="J44" t="n">
-        <v>978.5294117647059</v>
+        <v>1470</v>
       </c>
       <c r="K44" t="n">
         <v>0.8723607647650184</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.482315</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.232628</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0.1225</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0.281468</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0.7527430000000001</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0.566621</v>
       </c>
     </row>
     <row r="45">
@@ -2073,7 +3011,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2083,22 +3021,43 @@
         <v>29.26618143551284</v>
       </c>
       <c r="F45" t="n">
-        <v>15.3764705882353</v>
+        <v>18.4</v>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="H45" t="n">
         <v>577.7141136657015</v>
       </c>
       <c r="I45" t="n">
-        <v>0.3341013126108796</v>
+        <v>0.334101</v>
       </c>
       <c r="J45" t="n">
-        <v>978.5294117647059</v>
+        <v>1470</v>
       </c>
       <c r="K45" t="n">
         <v>0.8630879941049661</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.482315</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.232628</v>
+      </c>
+      <c r="N45" t="n">
+        <v>1</v>
+      </c>
+      <c r="O45" t="n">
+        <v>1</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0.111624</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0.7527430000000001</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0.566621</v>
       </c>
     </row>
     <row r="46">
@@ -2110,7 +3069,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2120,7 +3079,7 @@
         <v>29.27904871198617</v>
       </c>
       <c r="F46" t="n">
-        <v>15.3764705882353</v>
+        <v>18.4</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -2129,13 +3088,34 @@
         <v>329.1537609913248</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1903548848758864</v>
+        <v>0.190355</v>
       </c>
       <c r="J46" t="n">
-        <v>978.5294117647059</v>
+        <v>1470</v>
       </c>
       <c r="K46" t="n">
         <v>0.8042170793660591</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.482315</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.232628</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0.036235</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0.7527430000000001</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0.566621</v>
       </c>
     </row>
     <row r="47">
@@ -2147,7 +3127,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2157,22 +3137,43 @@
         <v>29.28245213874217</v>
       </c>
       <c r="F47" t="n">
-        <v>15.3764705882353</v>
+        <v>18.4</v>
       </c>
       <c r="G47" t="n">
-        <v>0.5</v>
+        <v>0.35</v>
       </c>
       <c r="H47" t="n">
         <v>383.8029861424964</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2219594059084802</v>
+        <v>0.221959</v>
       </c>
       <c r="J47" t="n">
-        <v>978.5294117647059</v>
+        <v>1470</v>
       </c>
       <c r="K47" t="n">
         <v>0.8421509684646951</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.482315</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.232628</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0.1225</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0.049266</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0.7527430000000001</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0.566621</v>
       </c>
     </row>
     <row r="48">
@@ -2184,7 +3185,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2194,22 +3195,43 @@
         <v>29.26917774728668</v>
       </c>
       <c r="F48" t="n">
-        <v>15.3764705882353</v>
+        <v>18.4</v>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="H48" t="n">
         <v>956.6542417360873</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5532484499136586</v>
+        <v>0.553248</v>
       </c>
       <c r="J48" t="n">
-        <v>978.5294117647059</v>
+        <v>1470</v>
       </c>
       <c r="K48" t="n">
         <v>0.8551112403364411</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.482315</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.232628</v>
+      </c>
+      <c r="N48" t="n">
+        <v>1</v>
+      </c>
+      <c r="O48" t="n">
+        <v>1</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0.306084</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0.7527430000000001</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0.566621</v>
       </c>
     </row>
     <row r="49">
@@ -2221,7 +3243,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2231,7 +3253,7 @@
         <v>29.26881829375751</v>
       </c>
       <c r="F49" t="n">
-        <v>15.3764705882353</v>
+        <v>18.4</v>
       </c>
       <c r="G49" t="n">
         <v>0.5</v>
@@ -2240,13 +3262,34 @@
         <v>1063.635015551099</v>
       </c>
       <c r="I49" t="n">
-        <v>0.6151171425944221</v>
+        <v>0.615117</v>
       </c>
       <c r="J49" t="n">
-        <v>978.5294117647059</v>
+        <v>1470</v>
       </c>
       <c r="K49" t="n">
         <v>0.9309992901953763</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.482315</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.232628</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0.378369</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0.7527430000000001</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0.566621</v>
       </c>
     </row>
     <row r="50">
@@ -2258,7 +3301,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2268,22 +3311,43 @@
         <v>29.26868471951212</v>
       </c>
       <c r="F50" t="n">
-        <v>15.3764705882353</v>
+        <v>18.4</v>
       </c>
       <c r="G50" t="n">
-        <v>0.75</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="H50" t="n">
         <v>1041.287026554613</v>
       </c>
       <c r="I50" t="n">
-        <v>0.6021929430962253</v>
+        <v>0.602193</v>
       </c>
       <c r="J50" t="n">
-        <v>978.5294117647059</v>
+        <v>1470</v>
       </c>
       <c r="K50" t="n">
         <v>0.8953240933628536</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.482315</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.232628</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0.362636</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0.7527430000000001</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0.566621</v>
       </c>
     </row>
     <row r="51">
@@ -2295,7 +3359,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2305,22 +3369,43 @@
         <v>29.28747203799683</v>
       </c>
       <c r="F51" t="n">
-        <v>15.3764705882353</v>
+        <v>18.4</v>
       </c>
       <c r="G51" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="H51" t="n">
         <v>107.8927018871471</v>
       </c>
       <c r="I51" t="n">
-        <v>0.06239607527139121</v>
+        <v>0.062396</v>
       </c>
       <c r="J51" t="n">
-        <v>978.5294117647059</v>
+        <v>1470</v>
       </c>
       <c r="K51" t="n">
         <v>0.7899911711162938</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0.482315</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.232628</v>
+      </c>
+      <c r="N51" t="n">
+        <v>1</v>
+      </c>
+      <c r="O51" t="n">
+        <v>1</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0.003893</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0.7527430000000001</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0.566621</v>
       </c>
     </row>
     <row r="52">
@@ -2332,7 +3417,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>BATTALGAZİ</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2342,10 +3427,10 @@
         <v>29.28292602245544</v>
       </c>
       <c r="F52" t="n">
-        <v>15.3764705882353</v>
+        <v>18.4</v>
       </c>
       <c r="G52" t="n">
-        <v>0.75</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -2354,10 +3439,31 @@
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>978.5294117647059</v>
+        <v>1470</v>
       </c>
       <c r="K52" t="n">
         <v>0.8943473773541702</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0.482315</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0.232628</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0.7527430000000001</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0.566621</v>
       </c>
     </row>
     <row r="53">
@@ -2369,7 +3475,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FATİH</t>
+          <t>FATIH</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2379,22 +3485,43 @@
         <v>29.27340411193601</v>
       </c>
       <c r="F53" t="n">
-        <v>15.3764705882353</v>
+        <v>17</v>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="H53" t="n">
         <v>313.2560732040218</v>
       </c>
       <c r="I53" t="n">
-        <v>0.1811609977410996</v>
+        <v>0.181161</v>
       </c>
       <c r="J53" t="n">
-        <v>978.5294117647059</v>
+        <v>1112</v>
       </c>
       <c r="K53" t="n">
         <v>0.6417712694114809</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0.437299</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0.19123</v>
+      </c>
+      <c r="N53" t="n">
+        <v>1</v>
+      </c>
+      <c r="O53" t="n">
+        <v>1</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0.032819</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0.450633</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0.20307</v>
       </c>
     </row>
     <row r="54">
@@ -2406,7 +3533,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>FATİH</t>
+          <t>FATIH</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2416,22 +3543,43 @@
         <v>29.27276948431416</v>
       </c>
       <c r="F54" t="n">
-        <v>15.3764705882353</v>
+        <v>17</v>
       </c>
       <c r="G54" t="n">
-        <v>0.75</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="H54" t="n">
         <v>364.7230424989933</v>
       </c>
       <c r="I54" t="n">
-        <v>0.210925169311095</v>
+        <v>0.210925</v>
       </c>
       <c r="J54" t="n">
-        <v>978.5294117647059</v>
+        <v>1112</v>
       </c>
       <c r="K54" t="n">
         <v>0.6271792834169987</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0.437299</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.19123</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0.044489</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0.450633</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0.20307</v>
       </c>
     </row>
     <row r="55">
@@ -2443,7 +3591,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>FATİH</t>
+          <t>FATIH</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2453,22 +3601,43 @@
         <v>29.2790352494371</v>
       </c>
       <c r="F55" t="n">
-        <v>15.3764705882353</v>
+        <v>17</v>
       </c>
       <c r="G55" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="H55" t="n">
         <v>687.5974244142948</v>
       </c>
       <c r="I55" t="n">
-        <v>0.3976485888271189</v>
+        <v>0.397649</v>
       </c>
       <c r="J55" t="n">
-        <v>978.5294117647059</v>
+        <v>1112</v>
       </c>
       <c r="K55" t="n">
         <v>0.6916091978743401</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.437299</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.19123</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0.158124</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0.450633</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0.20307</v>
       </c>
     </row>
     <row r="56">
@@ -2480,7 +3649,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>FATİH</t>
+          <t>FATIH</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2490,22 +3659,43 @@
         <v>29.27456122232974</v>
       </c>
       <c r="F56" t="n">
-        <v>15.3764705882353</v>
+        <v>17</v>
       </c>
       <c r="G56" t="n">
-        <v>0.75</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="H56" t="n">
         <v>403.2750114742097</v>
       </c>
       <c r="I56" t="n">
-        <v>0.2332203896175994</v>
+        <v>0.23322</v>
       </c>
       <c r="J56" t="n">
-        <v>978.5294117647059</v>
+        <v>1112</v>
       </c>
       <c r="K56" t="n">
         <v>0.7125753595570942</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0.437299</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.19123</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0.054392</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0.450633</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0.20307</v>
       </c>
     </row>
     <row r="57">
@@ -2517,7 +3707,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>FATİH</t>
+          <t>FATIH</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2527,7 +3717,7 @@
         <v>29.28047733713997</v>
       </c>
       <c r="F57" t="n">
-        <v>15.3764705882353</v>
+        <v>17</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -2536,13 +3726,34 @@
         <v>792.5388888386593</v>
       </c>
       <c r="I57" t="n">
-        <v>0.4583379162680207</v>
+        <v>0.458338</v>
       </c>
       <c r="J57" t="n">
-        <v>978.5294117647059</v>
+        <v>1112</v>
       </c>
       <c r="K57" t="n">
         <v>0.7075893893881066</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0.437299</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.19123</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0.210074</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0.450633</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0.20307</v>
       </c>
     </row>
     <row r="58">
@@ -2554,7 +3765,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>FATİH</t>
+          <t>FATIH</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2564,22 +3775,43 @@
         <v>29.27955626200323</v>
       </c>
       <c r="F58" t="n">
-        <v>15.3764705882353</v>
+        <v>17</v>
       </c>
       <c r="G58" t="n">
-        <v>0.75</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="H58" t="n">
         <v>772.8352744652042</v>
       </c>
       <c r="I58" t="n">
-        <v>0.4469430009117391</v>
+        <v>0.446943</v>
       </c>
       <c r="J58" t="n">
-        <v>978.5294117647059</v>
+        <v>1112</v>
       </c>
       <c r="K58" t="n">
         <v>0.6190645072711647</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0.437299</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.19123</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0.199758</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0.450633</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0.20307</v>
       </c>
     </row>
     <row r="59">
@@ -2591,7 +3823,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>FATİH</t>
+          <t>FATIH</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2601,22 +3833,43 @@
         <v>29.27987065500061</v>
       </c>
       <c r="F59" t="n">
-        <v>15.3764705882353</v>
+        <v>17</v>
       </c>
       <c r="G59" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="H59" t="n">
         <v>645.0166787013479</v>
       </c>
       <c r="I59" t="n">
-        <v>0.3730234624919195</v>
+        <v>0.373023</v>
       </c>
       <c r="J59" t="n">
-        <v>978.5294117647059</v>
+        <v>1112</v>
       </c>
       <c r="K59" t="n">
         <v>0.6455647646397359</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0.437299</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0.19123</v>
+      </c>
+      <c r="N59" t="n">
+        <v>1</v>
+      </c>
+      <c r="O59" t="n">
+        <v>1</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0.139147</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0.450633</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0.20307</v>
       </c>
     </row>
     <row r="60">
@@ -2628,7 +3881,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>HAMİDİYE</t>
+          <t>HAMIDIYE</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2638,22 +3891,43 @@
         <v>29.29037663758628</v>
       </c>
       <c r="F60" t="n">
-        <v>15.3764705882353</v>
+        <v>32.7</v>
       </c>
       <c r="G60" t="n">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="H60" t="n">
         <v>876.8784467157899</v>
       </c>
       <c r="I60" t="n">
-        <v>0.5071128316201424</v>
+        <v>0.507113</v>
       </c>
       <c r="J60" t="n">
-        <v>978.5294117647059</v>
+        <v>1651</v>
       </c>
       <c r="K60" t="n">
         <v>0.6496401410357842</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0.942122</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.887594</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0.1225</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0.257163</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0.905485</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0.819904</v>
       </c>
     </row>
     <row r="61">
@@ -2665,7 +3939,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>HAMİDİYE</t>
+          <t>HAMIDIYE</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2675,7 +3949,7 @@
         <v>29.2900754188337</v>
       </c>
       <c r="F61" t="n">
-        <v>15.3764705882353</v>
+        <v>32.7</v>
       </c>
       <c r="G61" t="n">
         <v>0.5</v>
@@ -2684,13 +3958,34 @@
         <v>1102.887335100135</v>
       </c>
       <c r="I61" t="n">
-        <v>0.6378173868400444</v>
+        <v>0.637817</v>
       </c>
       <c r="J61" t="n">
-        <v>978.5294117647059</v>
+        <v>1651</v>
       </c>
       <c r="K61" t="n">
         <v>0.6818542258217239</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0.942122</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.887594</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0.406811</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0.905485</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0.819904</v>
       </c>
     </row>
     <row r="62">
@@ -2702,7 +3997,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>HAMİDİYE</t>
+          <t>HAMIDIYE</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2712,22 +4007,43 @@
         <v>29.28554628294502</v>
       </c>
       <c r="F62" t="n">
-        <v>15.3764705882353</v>
+        <v>32.7</v>
       </c>
       <c r="G62" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="H62" t="n">
         <v>789.9557153878218</v>
       </c>
       <c r="I62" t="n">
-        <v>0.4568440257429127</v>
+        <v>0.456844</v>
       </c>
       <c r="J62" t="n">
-        <v>978.5294117647059</v>
+        <v>1651</v>
       </c>
       <c r="K62" t="n">
         <v>0.6091182575733415</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0.942122</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0.887594</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0.208706</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0.905485</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0.819904</v>
       </c>
     </row>
     <row r="63">
@@ -2739,7 +4055,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>HAMİDİYE</t>
+          <t>HAMIDIYE</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2749,22 +4065,43 @@
         <v>29.28870336682376</v>
       </c>
       <c r="F63" t="n">
-        <v>15.3764705882353</v>
+        <v>32.7</v>
       </c>
       <c r="G63" t="n">
-        <v>0.75</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="H63" t="n">
         <v>979.2299576551808</v>
       </c>
       <c r="I63" t="n">
-        <v>0.5663043475337469</v>
+        <v>0.566304</v>
       </c>
       <c r="J63" t="n">
-        <v>978.5294117647059</v>
+        <v>1651</v>
       </c>
       <c r="K63" t="n">
         <v>0.6237940206324152</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0.942122</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0.887594</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0.320701</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0.905485</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0.819904</v>
       </c>
     </row>
     <row r="64">
@@ -2776,7 +4113,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>HASANPAŞA</t>
+          <t>HASANPASA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2786,7 +4123,7 @@
         <v>29.24991319728006</v>
       </c>
       <c r="F64" t="n">
-        <v>15.3764705882353</v>
+        <v>15.1</v>
       </c>
       <c r="G64" t="n">
         <v>0.5</v>
@@ -2795,13 +4132,34 @@
         <v>673.0503789410932</v>
       </c>
       <c r="I64" t="n">
-        <v>0.3892357997464298</v>
+        <v>0.389236</v>
       </c>
       <c r="J64" t="n">
-        <v>978.5294117647059</v>
+        <v>955</v>
       </c>
       <c r="K64" t="n">
         <v>0.707911693436899</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0.376206</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0.141531</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0.151505</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0.318143</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0.101215</v>
       </c>
     </row>
     <row r="65">
@@ -2813,7 +4171,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>HASANPAŞA</t>
+          <t>HASANPASA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2823,22 +4181,43 @@
         <v>29.24734214592582</v>
       </c>
       <c r="F65" t="n">
-        <v>15.3764705882353</v>
+        <v>15.1</v>
       </c>
       <c r="G65" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="H65" t="n">
         <v>679.2896034787154</v>
       </c>
       <c r="I65" t="n">
-        <v>0.3928440430944534</v>
+        <v>0.392844</v>
       </c>
       <c r="J65" t="n">
-        <v>978.5294117647059</v>
+        <v>955</v>
       </c>
       <c r="K65" t="n">
         <v>0.7034181109331669</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0.376206</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0.141531</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0.154326</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0.318143</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0.101215</v>
       </c>
     </row>
     <row r="66">
@@ -2850,7 +4229,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>HASANPAŞA</t>
+          <t>HASANPASA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2860,22 +4239,43 @@
         <v>29.24933066296468</v>
       </c>
       <c r="F66" t="n">
-        <v>15.3764705882353</v>
+        <v>15.1</v>
       </c>
       <c r="G66" t="n">
-        <v>0.75</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="H66" t="n">
         <v>259.910995945958</v>
       </c>
       <c r="I66" t="n">
-        <v>0.1503106862952533</v>
+        <v>0.150311</v>
       </c>
       <c r="J66" t="n">
-        <v>978.5294117647059</v>
+        <v>955</v>
       </c>
       <c r="K66" t="n">
         <v>0.8038547332569104</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0.376206</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0.141531</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0.022593</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0.318143</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0.101215</v>
       </c>
     </row>
     <row r="67">
@@ -2887,7 +4287,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>HASANPAŞA</t>
+          <t>HASANPASA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2897,22 +4297,43 @@
         <v>29.25036418037588</v>
       </c>
       <c r="F67" t="n">
-        <v>15.3764705882353</v>
+        <v>15.1</v>
       </c>
       <c r="G67" t="n">
-        <v>0.75</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="H67" t="n">
         <v>405.0096033410726</v>
       </c>
       <c r="I67" t="n">
-        <v>0.2342235318394257</v>
+        <v>0.234224</v>
       </c>
       <c r="J67" t="n">
-        <v>978.5294117647059</v>
+        <v>955</v>
       </c>
       <c r="K67" t="n">
         <v>0.8310404435657416</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0.376206</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0.141531</v>
+      </c>
+      <c r="N67" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0.054861</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0.318143</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0.101215</v>
       </c>
     </row>
     <row r="68">
@@ -2924,7 +4345,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>HASANPAŞA</t>
+          <t>HASANPASA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2934,7 +4355,7 @@
         <v>29.24499981273058</v>
       </c>
       <c r="F68" t="n">
-        <v>15.3764705882353</v>
+        <v>15.1</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2943,13 +4364,34 @@
         <v>689.546161887431</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3987755748783643</v>
+        <v>0.398776</v>
       </c>
       <c r="J68" t="n">
-        <v>978.5294117647059</v>
+        <v>955</v>
       </c>
       <c r="K68" t="n">
         <v>0.7596279360581837</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0.376206</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0.141531</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" t="n">
+        <v>0.159022</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0.318143</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0.101215</v>
       </c>
     </row>
     <row r="69">
@@ -2961,7 +4403,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>HASANPAŞA</t>
+          <t>HASANPASA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2971,10 +4413,10 @@
         <v>29.25230054133037</v>
       </c>
       <c r="F69" t="n">
-        <v>15.3764705882353</v>
+        <v>15.1</v>
       </c>
       <c r="G69" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2983,10 +4425,31 @@
         <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>978.5294117647059</v>
+        <v>955</v>
       </c>
       <c r="K69" t="n">
         <v>0.8134050870318016</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0.376206</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0.141531</v>
+      </c>
+      <c r="N69" t="n">
+        <v>1</v>
+      </c>
+      <c r="O69" t="n">
+        <v>1</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0.318143</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0.101215</v>
       </c>
     </row>
     <row r="70">
@@ -2998,7 +4461,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>HASANPAŞA</t>
+          <t>HASANPASA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -3008,7 +4471,7 @@
         <v>29.24990969498234</v>
       </c>
       <c r="F70" t="n">
-        <v>15.3764705882353</v>
+        <v>15.1</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -3017,13 +4480,34 @@
         <v>253.1362725755004</v>
       </c>
       <c r="I70" t="n">
-        <v>0.1463927554067668</v>
+        <v>0.146393</v>
       </c>
       <c r="J70" t="n">
-        <v>978.5294117647059</v>
+        <v>955</v>
       </c>
       <c r="K70" t="n">
         <v>0.7813102433895821</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0.376206</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0.141531</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="n">
+        <v>0.021431</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0.318143</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0.101215</v>
       </c>
     </row>
     <row r="71">
@@ -3035,7 +4519,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MECİDİYE</t>
+          <t>MECIDIYE</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -3045,22 +4529,43 @@
         <v>29.29615807880041</v>
       </c>
       <c r="F71" t="n">
-        <v>15.3764705882353</v>
+        <v>15.5</v>
       </c>
       <c r="G71" t="n">
-        <v>0.75</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="H71" t="n">
         <v>992.9938905589755</v>
       </c>
       <c r="I71" t="n">
-        <v>0.5742642500894717</v>
+        <v>0.574264</v>
       </c>
       <c r="J71" t="n">
-        <v>978.5294117647059</v>
+        <v>1075</v>
       </c>
       <c r="K71" t="n">
         <v>0.6363768217731689</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0.389068</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0.151374</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0.329779</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0.419409</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0.175904</v>
       </c>
     </row>
     <row r="72">
@@ -3072,7 +4577,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MECİDİYE</t>
+          <t>MECIDIYE</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -3082,22 +4587,43 @@
         <v>29.30894031705047</v>
       </c>
       <c r="F72" t="n">
-        <v>15.3764705882353</v>
+        <v>15.5</v>
       </c>
       <c r="G72" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="H72" t="n">
         <v>710.9543091351767</v>
       </c>
       <c r="I72" t="n">
-        <v>0.4111562488602668</v>
+        <v>0.411156</v>
       </c>
       <c r="J72" t="n">
-        <v>978.5294117647059</v>
+        <v>1075</v>
       </c>
       <c r="K72" t="n">
         <v>0.6867025897788458</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0.389068</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0.151374</v>
+      </c>
+      <c r="N72" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="P72" t="n">
+        <v>0.169049</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0.419409</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0.175904</v>
       </c>
     </row>
     <row r="73">
@@ -3109,7 +4635,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MECİDİYE</t>
+          <t>MECIDIYE</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -3119,22 +4645,43 @@
         <v>29.30127930387404</v>
       </c>
       <c r="F73" t="n">
-        <v>15.3764705882353</v>
+        <v>15.5</v>
       </c>
       <c r="G73" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="H73" t="n">
         <v>647.6022304170159</v>
       </c>
       <c r="I73" t="n">
-        <v>0.37451872840562</v>
+        <v>0.374519</v>
       </c>
       <c r="J73" t="n">
-        <v>978.5294117647059</v>
+        <v>1075</v>
       </c>
       <c r="K73" t="n">
         <v>0.7455346378267236</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0.389068</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0.151374</v>
+      </c>
+      <c r="N73" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0.140264</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0.419409</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0.175904</v>
       </c>
     </row>
     <row r="74">
@@ -3146,7 +4693,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MECİDİYE</t>
+          <t>MECIDIYE</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3156,10 +4703,10 @@
         <v>29.29883972870045</v>
       </c>
       <c r="F74" t="n">
-        <v>15.3764705882353</v>
+        <v>15.5</v>
       </c>
       <c r="G74" t="n">
-        <v>0.75</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="H74" t="n">
         <v>1729.158467385467</v>
@@ -3168,10 +4715,31 @@
         <v>1</v>
       </c>
       <c r="J74" t="n">
-        <v>978.5294117647059</v>
+        <v>1075</v>
       </c>
       <c r="K74" t="n">
         <v>0.6668415075479275</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0.389068</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0.151374</v>
+      </c>
+      <c r="N74" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="P74" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0.419409</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0.175904</v>
       </c>
     </row>
     <row r="75">
@@ -3183,7 +4751,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MECİDİYE</t>
+          <t>MECIDIYE</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3193,22 +4761,43 @@
         <v>29.3077878511184</v>
       </c>
       <c r="F75" t="n">
-        <v>15.3764705882353</v>
+        <v>15.5</v>
       </c>
       <c r="G75" t="n">
-        <v>0.75</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="H75" t="n">
         <v>680.7495528754498</v>
       </c>
       <c r="I75" t="n">
-        <v>0.3936883551828312</v>
+        <v>0.393688</v>
       </c>
       <c r="J75" t="n">
-        <v>978.5294117647059</v>
+        <v>1075</v>
       </c>
       <c r="K75" t="n">
         <v>0.7468649922941254</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.389068</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.151374</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0.154991</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0.419409</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0.175904</v>
       </c>
     </row>
     <row r="76">
@@ -3220,7 +4809,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>MECİDİYE</t>
+          <t>MECIDIYE</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3230,7 +4819,7 @@
         <v>29.29691401533784</v>
       </c>
       <c r="F76" t="n">
-        <v>15.3764705882353</v>
+        <v>15.5</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -3239,13 +4828,34 @@
         <v>1574.9952774705</v>
       </c>
       <c r="I76" t="n">
-        <v>0.9108449613943909</v>
+        <v>0.910845</v>
       </c>
       <c r="J76" t="n">
-        <v>978.5294117647059</v>
+        <v>1075</v>
       </c>
       <c r="K76" t="n">
         <v>0.5376455542989378</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0.389068</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0.151374</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0.829639</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0.419409</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0.175904</v>
       </c>
     </row>
     <row r="77">
@@ -3257,7 +4867,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>MECİDİYE</t>
+          <t>MECIDIYE</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3267,22 +4877,43 @@
         <v>29.30838746812863</v>
       </c>
       <c r="F77" t="n">
-        <v>15.3764705882353</v>
+        <v>15.5</v>
       </c>
       <c r="G77" t="n">
-        <v>0.75</v>
+        <v>0.8499999999999999</v>
       </c>
       <c r="H77" t="n">
         <v>696.6007590323007</v>
       </c>
       <c r="I77" t="n">
-        <v>0.4028553612472426</v>
+        <v>0.402855</v>
       </c>
       <c r="J77" t="n">
-        <v>978.5294117647059</v>
+        <v>1075</v>
       </c>
       <c r="K77" t="n">
         <v>0.7097279347221863</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0.389068</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0.151374</v>
+      </c>
+      <c r="N77" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0.7225</v>
+      </c>
+      <c r="P77" t="n">
+        <v>0.162292</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>0.419409</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0.175904</v>
       </c>
     </row>
     <row r="78">
@@ -3294,7 +4925,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MECİDİYE</t>
+          <t>MECIDIYE</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3304,22 +4935,43 @@
         <v>29.30530226688093</v>
       </c>
       <c r="F78" t="n">
-        <v>15.3764705882353</v>
+        <v>15.5</v>
       </c>
       <c r="G78" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="H78" t="n">
         <v>1003.403364079733</v>
       </c>
       <c r="I78" t="n">
-        <v>0.5802842151285907</v>
+        <v>0.580284</v>
       </c>
       <c r="J78" t="n">
-        <v>978.5294117647059</v>
+        <v>1075</v>
       </c>
       <c r="K78" t="n">
         <v>0.6729851629153336</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0.389068</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0.151374</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0.2025</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0.33673</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>0.419409</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0.175904</v>
       </c>
     </row>
     <row r="79">
@@ -3331,7 +4983,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>MECİDİYE</t>
+          <t>MECIDIYE</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3341,7 +4993,7 @@
         <v>29.29838248815435</v>
       </c>
       <c r="F79" t="n">
-        <v>15.3764705882353</v>
+        <v>15.5</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -3350,13 +5002,34 @@
         <v>847.4788217028126</v>
       </c>
       <c r="I79" t="n">
-        <v>0.4901105582209725</v>
+        <v>0.490111</v>
       </c>
       <c r="J79" t="n">
-        <v>978.5294117647059</v>
+        <v>1075</v>
       </c>
       <c r="K79" t="n">
         <v>0.6536824419801317</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0.389068</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0.151374</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0.240208</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>0.419409</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0.175904</v>
       </c>
     </row>
     <row r="80">
@@ -3368,7 +5041,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>MECİDİYE</t>
+          <t>MECIDIYE</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3378,7 +5051,7 @@
         <v>29.29275014093141</v>
       </c>
       <c r="F80" t="n">
-        <v>15.3764705882353</v>
+        <v>15.5</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -3387,13 +5060,34 @@
         <v>1523.995373789485</v>
       </c>
       <c r="I80" t="n">
-        <v>0.8813509013397748</v>
+        <v>0.881351</v>
       </c>
       <c r="J80" t="n">
-        <v>978.5294117647059</v>
+        <v>1075</v>
       </c>
       <c r="K80" t="n">
         <v>0.6732208483302002</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0.389068</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0.151374</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0.776779</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>0.419409</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0.175904</v>
       </c>
     </row>
     <row r="81">
@@ -3405,7 +5099,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>MEHMET AKİF</t>
+          <t>MEHMET AKIF</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3415,7 +5109,7 @@
         <v>29.26739039582964</v>
       </c>
       <c r="F81" t="n">
-        <v>15.3764705882353</v>
+        <v>31</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -3424,13 +5118,34 @@
         <v>469.4887248138019</v>
       </c>
       <c r="I81" t="n">
-        <v>0.271512839146363</v>
+        <v>0.271513</v>
       </c>
       <c r="J81" t="n">
-        <v>978.5294117647059</v>
+        <v>1581</v>
       </c>
       <c r="K81" t="n">
         <v>0.5968408830975074</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0.88746</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0.787585</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0.07371900000000001</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>0.846414</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0.7164160000000001</v>
       </c>
     </row>
     <row r="82">
@@ -3442,7 +5157,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>MEHMET AKİF</t>
+          <t>MEHMET AKIF</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3452,22 +5167,43 @@
         <v>29.25809927583689</v>
       </c>
       <c r="F82" t="n">
-        <v>15.3764705882353</v>
+        <v>31</v>
       </c>
       <c r="G82" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="H82" t="n">
         <v>476.0728664258588</v>
       </c>
       <c r="I82" t="n">
-        <v>0.2753205535555647</v>
+        <v>0.275321</v>
       </c>
       <c r="J82" t="n">
-        <v>978.5294117647059</v>
+        <v>1581</v>
       </c>
       <c r="K82" t="n">
         <v>0.6852357344356764</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0.88746</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0.787585</v>
+      </c>
+      <c r="N82" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="P82" t="n">
+        <v>0.07580099999999999</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>0.846414</v>
+      </c>
+      <c r="R82" t="n">
+        <v>0.7164160000000001</v>
       </c>
     </row>
     <row r="83">
@@ -3479,7 +5215,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>MEHMET AKİF</t>
+          <t>MEHMET AKIF</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3489,7 +5225,7 @@
         <v>29.26498785648325</v>
       </c>
       <c r="F83" t="n">
-        <v>15.3764705882353</v>
+        <v>31</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -3498,13 +5234,34 @@
         <v>208.5042825671117</v>
       </c>
       <c r="I83" t="n">
-        <v>0.1205813616853611</v>
+        <v>0.120581</v>
       </c>
       <c r="J83" t="n">
-        <v>978.5294117647059</v>
+        <v>1581</v>
       </c>
       <c r="K83" t="n">
         <v>0.7140749574031393</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0.88746</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0.787585</v>
+      </c>
+      <c r="N83" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" t="n">
+        <v>0.01454</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>0.846414</v>
+      </c>
+      <c r="R83" t="n">
+        <v>0.7164160000000001</v>
       </c>
     </row>
     <row r="84">
@@ -3516,7 +5273,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>MEHMET AKİF</t>
+          <t>MEHMET AKIF</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3526,22 +5283,43 @@
         <v>29.26442884010378</v>
       </c>
       <c r="F84" t="n">
-        <v>15.3764705882353</v>
+        <v>31</v>
       </c>
       <c r="G84" t="n">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="H84" t="n">
         <v>839.5420413236531</v>
       </c>
       <c r="I84" t="n">
-        <v>0.4855205911769686</v>
+        <v>0.485521</v>
       </c>
       <c r="J84" t="n">
-        <v>978.5294117647059</v>
+        <v>1581</v>
       </c>
       <c r="K84" t="n">
         <v>0.7701140310646278</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0.88746</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0.787585</v>
+      </c>
+      <c r="N84" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0.1225</v>
+      </c>
+      <c r="P84" t="n">
+        <v>0.23573</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>0.846414</v>
+      </c>
+      <c r="R84" t="n">
+        <v>0.7164160000000001</v>
       </c>
     </row>
     <row r="85">
@@ -3553,7 +5331,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>MEHMET AKİF</t>
+          <t>MEHMET AKIF</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3563,10 +5341,10 @@
         <v>29.26311075774533</v>
       </c>
       <c r="F85" t="n">
-        <v>15.3764705882353</v>
+        <v>31</v>
       </c>
       <c r="G85" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -3575,10 +5353,31 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>978.5294117647059</v>
+        <v>1581</v>
       </c>
       <c r="K85" t="n">
         <v>0.6703058179138697</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0.88746</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0.787585</v>
+      </c>
+      <c r="N85" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="P85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>0.846414</v>
+      </c>
+      <c r="R85" t="n">
+        <v>0.7164160000000001</v>
       </c>
     </row>
     <row r="86">
@@ -3590,7 +5389,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>MEHMET AKİF</t>
+          <t>MEHMET AKIF</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3600,10 +5399,10 @@
         <v>29.26740035418011</v>
       </c>
       <c r="F86" t="n">
-        <v>15.3764705882353</v>
+        <v>31</v>
       </c>
       <c r="G86" t="n">
-        <v>0.75</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -3612,10 +5411,31 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>978.5294117647059</v>
+        <v>1581</v>
       </c>
       <c r="K86" t="n">
         <v>0.6557946486828926</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0.88746</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0.787585</v>
+      </c>
+      <c r="N86" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="P86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>0.846414</v>
+      </c>
+      <c r="R86" t="n">
+        <v>0.7164160000000001</v>
       </c>
     </row>
     <row r="87">
@@ -3627,7 +5447,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>MEHMET AKİF</t>
+          <t>MEHMET AKIF</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3637,7 +5457,7 @@
         <v>29.2654205704724</v>
       </c>
       <c r="F87" t="n">
-        <v>15.3764705882353</v>
+        <v>31</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -3646,13 +5466,34 @@
         <v>339.2996042641821</v>
       </c>
       <c r="I87" t="n">
-        <v>0.1962223883258149</v>
+        <v>0.196222</v>
       </c>
       <c r="J87" t="n">
-        <v>978.5294117647059</v>
+        <v>1581</v>
       </c>
       <c r="K87" t="n">
         <v>0.6711314766483252</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0.88746</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0.787585</v>
+      </c>
+      <c r="N87" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="n">
+        <v>0.038503</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>0.846414</v>
+      </c>
+      <c r="R87" t="n">
+        <v>0.7164160000000001</v>
       </c>
     </row>
     <row r="88">
@@ -3664,7 +5505,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>MEHMET AKİF</t>
+          <t>MEHMET AKIF</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3674,7 +5515,7 @@
         <v>29.26316269885574</v>
       </c>
       <c r="F88" t="n">
-        <v>15.3764705882353</v>
+        <v>31</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -3683,13 +5524,34 @@
         <v>184.2164234625406</v>
       </c>
       <c r="I88" t="n">
-        <v>0.1065353042749637</v>
+        <v>0.106535</v>
       </c>
       <c r="J88" t="n">
-        <v>978.5294117647059</v>
+        <v>1581</v>
       </c>
       <c r="K88" t="n">
         <v>0.7419894347126557</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0.88746</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0.787585</v>
+      </c>
+      <c r="N88" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" t="n">
+        <v>0.01135</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>0.846414</v>
+      </c>
+      <c r="R88" t="n">
+        <v>0.7164160000000001</v>
       </c>
     </row>
     <row r="89">
@@ -3701,7 +5563,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>MEHMET AKİF</t>
+          <t>MEHMET AKIF</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3711,22 +5573,43 @@
         <v>29.2652914567751</v>
       </c>
       <c r="F89" t="n">
-        <v>15.3764705882353</v>
+        <v>31</v>
       </c>
       <c r="G89" t="n">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="H89" t="n">
         <v>592.505132558926</v>
       </c>
       <c r="I89" t="n">
-        <v>0.3426551954227823</v>
+        <v>0.342655</v>
       </c>
       <c r="J89" t="n">
-        <v>978.5294117647059</v>
+        <v>1581</v>
       </c>
       <c r="K89" t="n">
         <v>0.7126568843105362</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0.88746</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0.787585</v>
+      </c>
+      <c r="N89" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0.1225</v>
+      </c>
+      <c r="P89" t="n">
+        <v>0.117413</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>0.846414</v>
+      </c>
+      <c r="R89" t="n">
+        <v>0.7164160000000001</v>
       </c>
     </row>
     <row r="90">
@@ -3738,7 +5621,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3748,22 +5631,43 @@
         <v>29.25587624905649</v>
       </c>
       <c r="F90" t="n">
-        <v>15.3764705882353</v>
+        <v>3.9</v>
       </c>
       <c r="G90" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="H90" t="n">
         <v>1032.197570890266</v>
       </c>
       <c r="I90" t="n">
-        <v>0.5969363654974754</v>
+        <v>0.596936</v>
       </c>
       <c r="J90" t="n">
-        <v>978.5294117647059</v>
+        <v>626</v>
       </c>
       <c r="K90" t="n">
         <v>0.9235119826066259</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0.016077</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0.000258</v>
+      </c>
+      <c r="N90" t="n">
+        <v>1</v>
+      </c>
+      <c r="O90" t="n">
+        <v>1</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0.356333</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>0.040506</v>
+      </c>
+      <c r="R90" t="n">
+        <v>0.001641</v>
       </c>
     </row>
     <row r="91">
@@ -3775,7 +5679,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3785,22 +5689,43 @@
         <v>29.28130344803975</v>
       </c>
       <c r="F91" t="n">
-        <v>15.3764705882353</v>
+        <v>3.9</v>
       </c>
       <c r="G91" t="n">
-        <v>0.75</v>
+        <v>0.8499999999999999</v>
       </c>
       <c r="H91" t="n">
         <v>1574.974869754613</v>
       </c>
       <c r="I91" t="n">
-        <v>0.9108331592858673</v>
+        <v>0.910833</v>
       </c>
       <c r="J91" t="n">
-        <v>978.5294117647059</v>
+        <v>626</v>
       </c>
       <c r="K91" t="n">
         <v>0.9756633644506456</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0.016077</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0.000258</v>
+      </c>
+      <c r="N91" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0.7225</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0.829617</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>0.040506</v>
+      </c>
+      <c r="R91" t="n">
+        <v>0.001641</v>
       </c>
     </row>
     <row r="92">
@@ -3812,7 +5737,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3822,22 +5747,43 @@
         <v>29.2673937473634</v>
       </c>
       <c r="F92" t="n">
-        <v>15.3764705882353</v>
+        <v>3.9</v>
       </c>
       <c r="G92" t="n">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="H92" t="n">
         <v>86.6807517222601</v>
       </c>
       <c r="I92" t="n">
-        <v>0.05012886520072603</v>
+        <v>0.050129</v>
       </c>
       <c r="J92" t="n">
-        <v>978.5294117647059</v>
+        <v>626</v>
       </c>
       <c r="K92" t="n">
         <v>0.9548538702623799</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0.016077</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0.000258</v>
+      </c>
+      <c r="N92" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0.1225</v>
+      </c>
+      <c r="P92" t="n">
+        <v>0.002513</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>0.040506</v>
+      </c>
+      <c r="R92" t="n">
+        <v>0.001641</v>
       </c>
     </row>
     <row r="93">
@@ -3849,7 +5795,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3859,22 +5805,43 @@
         <v>29.27425985345773</v>
       </c>
       <c r="F93" t="n">
-        <v>15.3764705882353</v>
+        <v>3.9</v>
       </c>
       <c r="G93" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="H93" t="n">
         <v>957.9619387172506</v>
       </c>
       <c r="I93" t="n">
-        <v>0.5540047119947972</v>
+        <v>0.554005</v>
       </c>
       <c r="J93" t="n">
-        <v>978.5294117647059</v>
+        <v>626</v>
       </c>
       <c r="K93" t="n">
         <v>0.99</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0.016077</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0.000258</v>
+      </c>
+      <c r="N93" t="n">
+        <v>1</v>
+      </c>
+      <c r="O93" t="n">
+        <v>1</v>
+      </c>
+      <c r="P93" t="n">
+        <v>0.306921</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>0.040506</v>
+      </c>
+      <c r="R93" t="n">
+        <v>0.001641</v>
       </c>
     </row>
     <row r="94">
@@ -3886,7 +5853,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3896,22 +5863,43 @@
         <v>29.26038178257916</v>
       </c>
       <c r="F94" t="n">
-        <v>15.3764705882353</v>
+        <v>3.9</v>
       </c>
       <c r="G94" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="H94" t="n">
         <v>667.5427218263897</v>
       </c>
       <c r="I94" t="n">
-        <v>0.3860506335406793</v>
+        <v>0.386051</v>
       </c>
       <c r="J94" t="n">
-        <v>978.5294117647059</v>
+        <v>626</v>
       </c>
       <c r="K94" t="n">
         <v>0.9148973381011102</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0.016077</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0.000258</v>
+      </c>
+      <c r="N94" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="P94" t="n">
+        <v>0.149035</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>0.040506</v>
+      </c>
+      <c r="R94" t="n">
+        <v>0.001641</v>
       </c>
     </row>
     <row r="95">
@@ -3923,7 +5911,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3933,7 +5921,7 @@
         <v>29.26072674144585</v>
       </c>
       <c r="F95" t="n">
-        <v>15.3764705882353</v>
+        <v>3.9</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -3942,13 +5930,34 @@
         <v>650.1822869692546</v>
       </c>
       <c r="I95" t="n">
-        <v>0.3760108163784128</v>
+        <v>0.376011</v>
       </c>
       <c r="J95" t="n">
-        <v>978.5294117647059</v>
+        <v>626</v>
       </c>
       <c r="K95" t="n">
         <v>0.9336168854650894</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0.016077</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0.000258</v>
+      </c>
+      <c r="N95" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
+      <c r="P95" t="n">
+        <v>0.141384</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>0.040506</v>
+      </c>
+      <c r="R95" t="n">
+        <v>0.001641</v>
       </c>
     </row>
     <row r="96">
@@ -3960,7 +5969,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3970,7 +5979,7 @@
         <v>29.25783125213962</v>
       </c>
       <c r="F96" t="n">
-        <v>15.3764705882353</v>
+        <v>3.9</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -3979,13 +5988,34 @@
         <v>857.2033229542557</v>
       </c>
       <c r="I96" t="n">
-        <v>0.4957343928404488</v>
+        <v>0.495734</v>
       </c>
       <c r="J96" t="n">
-        <v>978.5294117647059</v>
+        <v>626</v>
       </c>
       <c r="K96" t="n">
         <v>0.9303945851383699</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0.016077</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0.000258</v>
+      </c>
+      <c r="N96" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" t="n">
+        <v>0.245753</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>0.040506</v>
+      </c>
+      <c r="R96" t="n">
+        <v>0.001641</v>
       </c>
     </row>
     <row r="97">
@@ -3997,7 +6027,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -4007,22 +6037,43 @@
         <v>29.26270574448719</v>
       </c>
       <c r="F97" t="n">
-        <v>15.3764705882353</v>
+        <v>3.9</v>
       </c>
       <c r="G97" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="H97" t="n">
         <v>816.9503690993223</v>
       </c>
       <c r="I97" t="n">
-        <v>0.4724554657703366</v>
+        <v>0.472455</v>
       </c>
       <c r="J97" t="n">
-        <v>978.5294117647059</v>
+        <v>626</v>
       </c>
       <c r="K97" t="n">
         <v>0.8768242453883719</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0.016077</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0.000258</v>
+      </c>
+      <c r="N97" t="n">
+        <v>1</v>
+      </c>
+      <c r="O97" t="n">
+        <v>1</v>
+      </c>
+      <c r="P97" t="n">
+        <v>0.223214</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>0.040506</v>
+      </c>
+      <c r="R97" t="n">
+        <v>0.001641</v>
       </c>
     </row>
     <row r="98">
@@ -4034,7 +6085,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -4044,22 +6095,43 @@
         <v>29.26816415735592</v>
       </c>
       <c r="F98" t="n">
-        <v>15.3764705882353</v>
+        <v>3.9</v>
       </c>
       <c r="G98" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="H98" t="n">
         <v>1242.285452607057</v>
       </c>
       <c r="I98" t="n">
-        <v>0.7184335479011504</v>
+        <v>0.718434</v>
       </c>
       <c r="J98" t="n">
-        <v>978.5294117647059</v>
+        <v>626</v>
       </c>
       <c r="K98" t="n">
         <v>0.9648060066482066</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0.016077</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0.000258</v>
+      </c>
+      <c r="N98" t="n">
+        <v>1</v>
+      </c>
+      <c r="O98" t="n">
+        <v>1</v>
+      </c>
+      <c r="P98" t="n">
+        <v>0.516147</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>0.040506</v>
+      </c>
+      <c r="R98" t="n">
+        <v>0.001641</v>
       </c>
     </row>
     <row r="99">
@@ -4071,7 +6143,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -4081,22 +6153,43 @@
         <v>29.26421671103377</v>
       </c>
       <c r="F99" t="n">
-        <v>15.3764705882353</v>
+        <v>3.9</v>
       </c>
       <c r="G99" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="H99" t="n">
         <v>354.5314182296436</v>
       </c>
       <c r="I99" t="n">
-        <v>0.2050311899786168</v>
+        <v>0.205031</v>
       </c>
       <c r="J99" t="n">
-        <v>978.5294117647059</v>
+        <v>626</v>
       </c>
       <c r="K99" t="n">
         <v>0.9630527564039723</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0.016077</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0.000258</v>
+      </c>
+      <c r="N99" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="P99" t="n">
+        <v>0.042038</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>0.040506</v>
+      </c>
+      <c r="R99" t="n">
+        <v>0.001641</v>
       </c>
     </row>
     <row r="100">
@@ -4108,7 +6201,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -4118,22 +6211,43 @@
         <v>29.2740647093532</v>
       </c>
       <c r="F100" t="n">
-        <v>15.3764705882353</v>
+        <v>3.9</v>
       </c>
       <c r="G100" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="H100" t="n">
         <v>545.5310345545806</v>
       </c>
       <c r="I100" t="n">
-        <v>0.3154893231847268</v>
+        <v>0.315489</v>
       </c>
       <c r="J100" t="n">
-        <v>978.5294117647059</v>
+        <v>626</v>
       </c>
       <c r="K100" t="n">
         <v>0.9502556656271008</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0.016077</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0.000258</v>
+      </c>
+      <c r="N100" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="P100" t="n">
+        <v>0.099534</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>0.040506</v>
+      </c>
+      <c r="R100" t="n">
+        <v>0.001641</v>
       </c>
     </row>
     <row r="101">
@@ -4145,7 +6259,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -4155,7 +6269,7 @@
         <v>29.27351612621354</v>
       </c>
       <c r="F101" t="n">
-        <v>15.3764705882353</v>
+        <v>3.9</v>
       </c>
       <c r="G101" t="n">
         <v>0.5</v>
@@ -4164,13 +6278,34 @@
         <v>494.5518151902769</v>
       </c>
       <c r="I101" t="n">
-        <v>0.2860072252013155</v>
+        <v>0.286007</v>
       </c>
       <c r="J101" t="n">
-        <v>978.5294117647059</v>
+        <v>626</v>
       </c>
       <c r="K101" t="n">
         <v>0.9382706361262205</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0.016077</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0.000258</v>
+      </c>
+      <c r="N101" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P101" t="n">
+        <v>0.0818</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>0.040506</v>
+      </c>
+      <c r="R101" t="n">
+        <v>0.001641</v>
       </c>
     </row>
     <row r="102">
@@ -4182,7 +6317,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -4192,22 +6327,43 @@
         <v>29.27780231557844</v>
       </c>
       <c r="F102" t="n">
-        <v>15.3764705882353</v>
+        <v>3.9</v>
       </c>
       <c r="G102" t="n">
-        <v>0.75</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="H102" t="n">
         <v>1166.396545942877</v>
       </c>
       <c r="I102" t="n">
-        <v>0.6745457793157034</v>
+        <v>0.674546</v>
       </c>
       <c r="J102" t="n">
-        <v>978.5294117647059</v>
+        <v>626</v>
       </c>
       <c r="K102" t="n">
         <v>0.8792314556924571</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0.016077</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0.000258</v>
+      </c>
+      <c r="N102" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="P102" t="n">
+        <v>0.455012</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>0.040506</v>
+      </c>
+      <c r="R102" t="n">
+        <v>0.001641</v>
       </c>
     </row>
     <row r="103">
@@ -4219,7 +6375,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4229,22 +6385,43 @@
         <v>29.26045077125254</v>
       </c>
       <c r="F103" t="n">
-        <v>15.3764705882353</v>
+        <v>3.9</v>
       </c>
       <c r="G103" t="n">
-        <v>0.75</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="H103" t="n">
         <v>633.8354309475709</v>
       </c>
       <c r="I103" t="n">
-        <v>0.3665571680691282</v>
+        <v>0.366557</v>
       </c>
       <c r="J103" t="n">
-        <v>978.5294117647059</v>
+        <v>626</v>
       </c>
       <c r="K103" t="n">
         <v>0.9289677266567099</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0.016077</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0.000258</v>
+      </c>
+      <c r="N103" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="P103" t="n">
+        <v>0.134364</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>0.040506</v>
+      </c>
+      <c r="R103" t="n">
+        <v>0.001641</v>
       </c>
     </row>
     <row r="104">
@@ -4256,7 +6433,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4266,22 +6443,43 @@
         <v>29.26895176772889</v>
       </c>
       <c r="F104" t="n">
-        <v>15.3764705882353</v>
+        <v>3.9</v>
       </c>
       <c r="G104" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="H104" t="n">
         <v>174.2351018346841</v>
       </c>
       <c r="I104" t="n">
-        <v>0.1007629463239029</v>
+        <v>0.100763</v>
       </c>
       <c r="J104" t="n">
-        <v>978.5294117647059</v>
+        <v>626</v>
       </c>
       <c r="K104" t="n">
         <v>0.9328642669686393</v>
+      </c>
+      <c r="L104" t="n">
+        <v>0.016077</v>
+      </c>
+      <c r="M104" t="n">
+        <v>0.000258</v>
+      </c>
+      <c r="N104" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="P104" t="n">
+        <v>0.010153</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>0.040506</v>
+      </c>
+      <c r="R104" t="n">
+        <v>0.001641</v>
       </c>
     </row>
     <row r="105">
@@ -4293,7 +6491,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4303,22 +6501,43 @@
         <v>29.27133179305416</v>
       </c>
       <c r="F105" t="n">
-        <v>15.3764705882353</v>
+        <v>3.9</v>
       </c>
       <c r="G105" t="n">
-        <v>0.75</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="H105" t="n">
         <v>432.5430810698456</v>
       </c>
       <c r="I105" t="n">
-        <v>0.2501465824146598</v>
+        <v>0.250147</v>
       </c>
       <c r="J105" t="n">
-        <v>978.5294117647059</v>
+        <v>626</v>
       </c>
       <c r="K105" t="n">
         <v>0.9098861293338969</v>
+      </c>
+      <c r="L105" t="n">
+        <v>0.016077</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0.000258</v>
+      </c>
+      <c r="N105" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="P105" t="n">
+        <v>0.062573</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>0.040506</v>
+      </c>
+      <c r="R105" t="n">
+        <v>0.001641</v>
       </c>
     </row>
     <row r="106">
@@ -4330,7 +6549,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4340,22 +6559,43 @@
         <v>29.28371064633141</v>
       </c>
       <c r="F106" t="n">
-        <v>15.3764705882353</v>
+        <v>3.9</v>
       </c>
       <c r="G106" t="n">
-        <v>0.75</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="H106" t="n">
         <v>1472.800594962503</v>
       </c>
       <c r="I106" t="n">
-        <v>0.8517441418711705</v>
+        <v>0.8517439999999999</v>
       </c>
       <c r="J106" t="n">
-        <v>978.5294117647059</v>
+        <v>626</v>
       </c>
       <c r="K106" t="n">
         <v>0.9419357072116774</v>
+      </c>
+      <c r="L106" t="n">
+        <v>0.016077</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0.000258</v>
+      </c>
+      <c r="N106" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="P106" t="n">
+        <v>0.725468</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>0.040506</v>
+      </c>
+      <c r="R106" t="n">
+        <v>0.001641</v>
       </c>
     </row>
     <row r="107">
@@ -4367,7 +6607,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4377,22 +6617,43 @@
         <v>29.27280938279549</v>
       </c>
       <c r="F107" t="n">
-        <v>15.3764705882353</v>
+        <v>3.9</v>
       </c>
       <c r="G107" t="n">
-        <v>0.75</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="H107" t="n">
         <v>516.403135223708</v>
       </c>
       <c r="I107" t="n">
-        <v>0.2986441930938366</v>
+        <v>0.298644</v>
       </c>
       <c r="J107" t="n">
-        <v>978.5294117647059</v>
+        <v>626</v>
       </c>
       <c r="K107" t="n">
         <v>0.9702025356357047</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0.016077</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0.000258</v>
+      </c>
+      <c r="N107" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="P107" t="n">
+        <v>0.089188</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>0.040506</v>
+      </c>
+      <c r="R107" t="n">
+        <v>0.001641</v>
       </c>
     </row>
     <row r="108">
@@ -4404,7 +6665,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4414,22 +6675,43 @@
         <v>29.27398646683528</v>
       </c>
       <c r="F108" t="n">
-        <v>15.3764705882353</v>
+        <v>3.9</v>
       </c>
       <c r="G108" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="H108" t="n">
         <v>835.6680594423433</v>
       </c>
       <c r="I108" t="n">
-        <v>0.4832802054897231</v>
+        <v>0.48328</v>
       </c>
       <c r="J108" t="n">
-        <v>978.5294117647059</v>
+        <v>626</v>
       </c>
       <c r="K108" t="n">
         <v>0.99</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0.016077</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0.000258</v>
+      </c>
+      <c r="N108" t="n">
+        <v>1</v>
+      </c>
+      <c r="O108" t="n">
+        <v>1</v>
+      </c>
+      <c r="P108" t="n">
+        <v>0.23356</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>0.040506</v>
+      </c>
+      <c r="R108" t="n">
+        <v>0.001641</v>
       </c>
     </row>
     <row r="109">
@@ -4441,7 +6723,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4451,10 +6733,10 @@
         <v>29.26799970752074</v>
       </c>
       <c r="F109" t="n">
-        <v>15.3764705882353</v>
+        <v>3.9</v>
       </c>
       <c r="G109" t="n">
-        <v>0.75</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -4463,10 +6745,31 @@
         <v>0</v>
       </c>
       <c r="J109" t="n">
-        <v>978.5294117647059</v>
+        <v>626</v>
       </c>
       <c r="K109" t="n">
         <v>0.9587288834365698</v>
+      </c>
+      <c r="L109" t="n">
+        <v>0.016077</v>
+      </c>
+      <c r="M109" t="n">
+        <v>0.000258</v>
+      </c>
+      <c r="N109" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="P109" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>0.040506</v>
+      </c>
+      <c r="R109" t="n">
+        <v>0.001641</v>
       </c>
     </row>
     <row r="110">
@@ -4478,7 +6781,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4488,22 +6791,43 @@
         <v>29.25990016183826</v>
       </c>
       <c r="F110" t="n">
-        <v>15.3764705882353</v>
+        <v>3.9</v>
       </c>
       <c r="G110" t="n">
-        <v>0.75</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="H110" t="n">
         <v>683.3538550714932</v>
       </c>
       <c r="I110" t="n">
-        <v>0.3951944647992512</v>
+        <v>0.395194</v>
       </c>
       <c r="J110" t="n">
-        <v>978.5294117647059</v>
+        <v>626</v>
       </c>
       <c r="K110" t="n">
         <v>0.9628775123311161</v>
+      </c>
+      <c r="L110" t="n">
+        <v>0.016077</v>
+      </c>
+      <c r="M110" t="n">
+        <v>0.000258</v>
+      </c>
+      <c r="N110" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O110" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="P110" t="n">
+        <v>0.156179</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>0.040506</v>
+      </c>
+      <c r="R110" t="n">
+        <v>0.001641</v>
       </c>
     </row>
     <row r="111">
@@ -4515,7 +6839,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4525,22 +6849,43 @@
         <v>29.26234614076155</v>
       </c>
       <c r="F111" t="n">
-        <v>15.3764705882353</v>
+        <v>3.9</v>
       </c>
       <c r="G111" t="n">
-        <v>0.75</v>
+        <v>0.8499999999999999</v>
       </c>
       <c r="H111" t="n">
         <v>708.3165294668914</v>
       </c>
       <c r="I111" t="n">
-        <v>0.409630778686169</v>
+        <v>0.409631</v>
       </c>
       <c r="J111" t="n">
-        <v>978.5294117647059</v>
+        <v>626</v>
       </c>
       <c r="K111" t="n">
         <v>0.9462776970066694</v>
+      </c>
+      <c r="L111" t="n">
+        <v>0.016077</v>
+      </c>
+      <c r="M111" t="n">
+        <v>0.000258</v>
+      </c>
+      <c r="N111" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="O111" t="n">
+        <v>0.7225</v>
+      </c>
+      <c r="P111" t="n">
+        <v>0.167797</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>0.040506</v>
+      </c>
+      <c r="R111" t="n">
+        <v>0.001641</v>
       </c>
     </row>
     <row r="112">
@@ -4552,7 +6897,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>MİMAR SİNAN</t>
+          <t>MIMAR SINAN</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4562,22 +6907,43 @@
         <v>29.27889296595766</v>
       </c>
       <c r="F112" t="n">
-        <v>15.3764705882353</v>
+        <v>3.9</v>
       </c>
       <c r="G112" t="n">
-        <v>0.75</v>
+        <v>0.8499999999999999</v>
       </c>
       <c r="H112" t="n">
         <v>1240.116321204808</v>
       </c>
       <c r="I112" t="n">
-        <v>0.7171791045154446</v>
+        <v>0.717179</v>
       </c>
       <c r="J112" t="n">
-        <v>978.5294117647059</v>
+        <v>626</v>
       </c>
       <c r="K112" t="n">
         <v>0.8540614320300257</v>
+      </c>
+      <c r="L112" t="n">
+        <v>0.016077</v>
+      </c>
+      <c r="M112" t="n">
+        <v>0.000258</v>
+      </c>
+      <c r="N112" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="O112" t="n">
+        <v>0.7225</v>
+      </c>
+      <c r="P112" t="n">
+        <v>0.514346</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>0.040506</v>
+      </c>
+      <c r="R112" t="n">
+        <v>0.001641</v>
       </c>
     </row>
     <row r="113">
@@ -4589,7 +6955,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>NECİP FAZIL</t>
+          <t>NECIP FAZIL</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4599,22 +6965,43 @@
         <v>29.27601773017532</v>
       </c>
       <c r="F113" t="n">
-        <v>15.3764705882353</v>
+        <v>17.6</v>
       </c>
       <c r="G113" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="H113" t="n">
         <v>295.9062119598132</v>
       </c>
       <c r="I113" t="n">
-        <v>0.1711272954683159</v>
+        <v>0.171127</v>
       </c>
       <c r="J113" t="n">
-        <v>978.5294117647059</v>
+        <v>1082</v>
       </c>
       <c r="K113" t="n">
         <v>0.5486743062275392</v>
+      </c>
+      <c r="L113" t="n">
+        <v>0.456592</v>
+      </c>
+      <c r="M113" t="n">
+        <v>0.208476</v>
+      </c>
+      <c r="N113" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="P113" t="n">
+        <v>0.029285</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>0.425316</v>
+      </c>
+      <c r="R113" t="n">
+        <v>0.180894</v>
       </c>
     </row>
     <row r="114">
@@ -4626,7 +7013,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>NECİP FAZIL</t>
+          <t>NECIP FAZIL</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4636,22 +7023,43 @@
         <v>29.27223612680491</v>
       </c>
       <c r="F114" t="n">
-        <v>15.3764705882353</v>
+        <v>17.6</v>
       </c>
       <c r="G114" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="H114" t="n">
         <v>583.1283180956766</v>
       </c>
       <c r="I114" t="n">
-        <v>0.3372324336342532</v>
+        <v>0.337232</v>
       </c>
       <c r="J114" t="n">
-        <v>978.5294117647059</v>
+        <v>1082</v>
       </c>
       <c r="K114" t="n">
         <v>0.5530115104970513</v>
+      </c>
+      <c r="L114" t="n">
+        <v>0.456592</v>
+      </c>
+      <c r="M114" t="n">
+        <v>0.208476</v>
+      </c>
+      <c r="N114" t="n">
+        <v>1</v>
+      </c>
+      <c r="O114" t="n">
+        <v>1</v>
+      </c>
+      <c r="P114" t="n">
+        <v>0.113726</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>0.425316</v>
+      </c>
+      <c r="R114" t="n">
+        <v>0.180894</v>
       </c>
     </row>
     <row r="115">
@@ -4663,7 +7071,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>NECİP FAZIL</t>
+          <t>NECIP FAZIL</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4673,10 +7081,10 @@
         <v>29.27358071445466</v>
       </c>
       <c r="F115" t="n">
-        <v>15.3764705882353</v>
+        <v>17.6</v>
       </c>
       <c r="G115" t="n">
-        <v>0.75</v>
+        <v>0.8499999999999999</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
@@ -4685,10 +7093,31 @@
         <v>0</v>
       </c>
       <c r="J115" t="n">
-        <v>978.5294117647059</v>
+        <v>1082</v>
       </c>
       <c r="K115" t="n">
         <v>0.6731621056242644</v>
+      </c>
+      <c r="L115" t="n">
+        <v>0.456592</v>
+      </c>
+      <c r="M115" t="n">
+        <v>0.208476</v>
+      </c>
+      <c r="N115" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="O115" t="n">
+        <v>0.7225</v>
+      </c>
+      <c r="P115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>0.425316</v>
+      </c>
+      <c r="R115" t="n">
+        <v>0.180894</v>
       </c>
     </row>
     <row r="116">
@@ -4700,7 +7129,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>NECİP FAZIL</t>
+          <t>NECIP FAZIL</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4710,7 +7139,7 @@
         <v>29.27549202574264</v>
       </c>
       <c r="F116" t="n">
-        <v>15.3764705882353</v>
+        <v>17.6</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -4719,13 +7148,34 @@
         <v>613.290968448951</v>
       </c>
       <c r="I116" t="n">
-        <v>0.3546759767924932</v>
+        <v>0.354676</v>
       </c>
       <c r="J116" t="n">
-        <v>978.5294117647059</v>
+        <v>1082</v>
       </c>
       <c r="K116" t="n">
         <v>0.5403819517609439</v>
+      </c>
+      <c r="L116" t="n">
+        <v>0.456592</v>
+      </c>
+      <c r="M116" t="n">
+        <v>0.208476</v>
+      </c>
+      <c r="N116" t="n">
+        <v>0</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0</v>
+      </c>
+      <c r="P116" t="n">
+        <v>0.125795</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>0.425316</v>
+      </c>
+      <c r="R116" t="n">
+        <v>0.180894</v>
       </c>
     </row>
     <row r="117">
@@ -4737,7 +7187,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>NECİP FAZIL</t>
+          <t>NECIP FAZIL</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4747,22 +7197,43 @@
         <v>29.28106724371641</v>
       </c>
       <c r="F117" t="n">
-        <v>15.3764705882353</v>
+        <v>17.6</v>
       </c>
       <c r="G117" t="n">
-        <v>0.75</v>
+        <v>0.8499999999999999</v>
       </c>
       <c r="H117" t="n">
         <v>712.773196102973</v>
       </c>
       <c r="I117" t="n">
-        <v>0.4122081402872836</v>
+        <v>0.412208</v>
       </c>
       <c r="J117" t="n">
-        <v>978.5294117647059</v>
+        <v>1082</v>
       </c>
       <c r="K117" t="n">
         <v>0.5650773671166807</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.456592</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.208476</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.7225</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.169916</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.425316</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.180894</v>
       </c>
     </row>
     <row r="118">
@@ -4774,7 +7245,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>NECİP FAZIL</t>
+          <t>NECIP FAZIL</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4784,22 +7255,43 @@
         <v>29.27316051435645</v>
       </c>
       <c r="F118" t="n">
-        <v>15.3764705882353</v>
+        <v>17.6</v>
       </c>
       <c r="G118" t="n">
-        <v>0.75</v>
+        <v>0.8499999999999999</v>
       </c>
       <c r="H118" t="n">
         <v>61.34427283830708</v>
       </c>
       <c r="I118" t="n">
-        <v>0.03547637419898318</v>
+        <v>0.035476</v>
       </c>
       <c r="J118" t="n">
-        <v>978.5294117647059</v>
+        <v>1082</v>
       </c>
       <c r="K118" t="n">
         <v>0.5482644115147379</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.456592</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.208476</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.7225</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.001259</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.425316</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.180894</v>
       </c>
     </row>
     <row r="119">
@@ -4811,7 +7303,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>NECİP FAZIL</t>
+          <t>NECIP FAZIL</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4821,7 +7313,7 @@
         <v>29.27702793890641</v>
       </c>
       <c r="F119" t="n">
-        <v>15.3764705882353</v>
+        <v>17.6</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -4830,13 +7322,34 @@
         <v>494.214066502061</v>
       </c>
       <c r="I119" t="n">
-        <v>0.2858118997325477</v>
+        <v>0.285812</v>
       </c>
       <c r="J119" t="n">
-        <v>978.5294117647059</v>
+        <v>1082</v>
       </c>
       <c r="K119" t="n">
         <v>0.4915660981190234</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.456592</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.208476</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.081688</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.425316</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.180894</v>
       </c>
     </row>
     <row r="120">
@@ -4848,7 +7361,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>NECİP FAZIL</t>
+          <t>NECIP FAZIL</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4858,7 +7371,7 @@
         <v>29.26823062915377</v>
       </c>
       <c r="F120" t="n">
-        <v>15.3764705882353</v>
+        <v>17.6</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -4867,13 +7380,34 @@
         <v>531.8611862097534</v>
       </c>
       <c r="I120" t="n">
-        <v>0.3075838312343585</v>
+        <v>0.307584</v>
       </c>
       <c r="J120" t="n">
-        <v>978.5294117647059</v>
+        <v>1082</v>
       </c>
       <c r="K120" t="n">
         <v>0.6071411407257511</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.456592</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.208476</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.094608</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.425316</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.180894</v>
       </c>
     </row>
     <row r="121">
@@ -4885,7 +7419,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ORHANGAZİ</t>
+          <t>ORHANGAZI</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4895,10 +7429,10 @@
         <v>29.29091708430066</v>
       </c>
       <c r="F121" t="n">
-        <v>15.3764705882353</v>
+        <v>19.5</v>
       </c>
       <c r="G121" t="n">
-        <v>0.75</v>
+        <v>0.8499999999999999</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -4907,10 +7441,31 @@
         <v>0</v>
       </c>
       <c r="J121" t="n">
-        <v>978.5294117647059</v>
+        <v>918</v>
       </c>
       <c r="K121" t="n">
         <v>0.6069181095069792</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.517685</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.267998</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.7225</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.28692</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.08232299999999999</v>
       </c>
     </row>
     <row r="122">
@@ -4922,7 +7477,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>ORHANGAZİ</t>
+          <t>ORHANGAZI</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4932,22 +7487,43 @@
         <v>29.28793089165473</v>
       </c>
       <c r="F122" t="n">
-        <v>15.3764705882353</v>
+        <v>19.5</v>
       </c>
       <c r="G122" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="H122" t="n">
         <v>260.8089259606562</v>
       </c>
       <c r="I122" t="n">
-        <v>0.1508299735853626</v>
+        <v>0.15083</v>
       </c>
       <c r="J122" t="n">
-        <v>978.5294117647059</v>
+        <v>918</v>
       </c>
       <c r="K122" t="n">
         <v>0.6088730552247928</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.517685</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.267998</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.02275</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.28692</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.08232299999999999</v>
       </c>
     </row>
     <row r="123">
@@ -4959,7 +7535,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>ORHANGAZİ</t>
+          <t>ORHANGAZI</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4969,22 +7545,43 @@
         <v>29.28994169313448</v>
       </c>
       <c r="F123" t="n">
-        <v>15.3764705882353</v>
+        <v>19.5</v>
       </c>
       <c r="G123" t="n">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="H123" t="n">
         <v>82.73121881648721</v>
       </c>
       <c r="I123" t="n">
-        <v>0.04784478714757646</v>
+        <v>0.047845</v>
       </c>
       <c r="J123" t="n">
-        <v>978.5294117647059</v>
+        <v>918</v>
       </c>
       <c r="K123" t="n">
         <v>0.5238520851329036</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.517685</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.267998</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.1225</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.002289</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.28692</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.08232299999999999</v>
       </c>
     </row>
     <row r="124">
@@ -4996,7 +7593,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>ORHANGAZİ</t>
+          <t>ORHANGAZI</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -5006,22 +7603,43 @@
         <v>29.28668369067791</v>
       </c>
       <c r="F124" t="n">
-        <v>15.3764705882353</v>
+        <v>19.5</v>
       </c>
       <c r="G124" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="H124" t="n">
         <v>356.6827624917942</v>
       </c>
       <c r="I124" t="n">
-        <v>0.2062753467766942</v>
+        <v>0.206275</v>
       </c>
       <c r="J124" t="n">
-        <v>978.5294117647059</v>
+        <v>918</v>
       </c>
       <c r="K124" t="n">
         <v>0.6394611734194455</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.517685</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.267998</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.04255</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.28692</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.08232299999999999</v>
       </c>
     </row>
     <row r="125">
@@ -5033,7 +7651,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>ORHANGAZİ</t>
+          <t>ORHANGAZI</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -5043,22 +7661,43 @@
         <v>29.29031702546167</v>
       </c>
       <c r="F125" t="n">
-        <v>15.3764705882353</v>
+        <v>19.5</v>
       </c>
       <c r="G125" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="H125" t="n">
         <v>63.97948845710972</v>
       </c>
       <c r="I125" t="n">
-        <v>0.03700036154225261</v>
+        <v>0.037</v>
       </c>
       <c r="J125" t="n">
-        <v>978.5294117647059</v>
+        <v>918</v>
       </c>
       <c r="K125" t="n">
         <v>0.4992289047330265</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.517685</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.267998</v>
+      </c>
+      <c r="N125" t="n">
+        <v>1</v>
+      </c>
+      <c r="O125" t="n">
+        <v>1</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.001369</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.28692</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.08232299999999999</v>
       </c>
     </row>
     <row r="126">
@@ -5070,7 +7709,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>ORHANGAZİ</t>
+          <t>ORHANGAZI</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -5080,22 +7719,43 @@
         <v>29.29105219148152</v>
       </c>
       <c r="F126" t="n">
-        <v>15.3764705882353</v>
+        <v>19.5</v>
       </c>
       <c r="G126" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="H126" t="n">
         <v>699.1770798570534</v>
       </c>
       <c r="I126" t="n">
-        <v>0.4043452887890763</v>
+        <v>0.404345</v>
       </c>
       <c r="J126" t="n">
-        <v>978.5294117647059</v>
+        <v>918</v>
       </c>
       <c r="K126" t="n">
         <v>0.5986643125626541</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.517685</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.267998</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.163495</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.28692</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.08232299999999999</v>
       </c>
     </row>
     <row r="127">
@@ -5107,7 +7767,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>ORHANGAZİ</t>
+          <t>ORHANGAZI</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -5117,22 +7777,43 @@
         <v>29.28769611603024</v>
       </c>
       <c r="F127" t="n">
-        <v>15.3764705882353</v>
+        <v>19.5</v>
       </c>
       <c r="G127" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="H127" t="n">
         <v>304.6837515518817</v>
       </c>
       <c r="I127" t="n">
-        <v>0.1762034870132935</v>
+        <v>0.176203</v>
       </c>
       <c r="J127" t="n">
-        <v>978.5294117647059</v>
+        <v>918</v>
       </c>
       <c r="K127" t="n">
         <v>0.6788442391631395</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.517685</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.267998</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.031048</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.28692</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.08232299999999999</v>
       </c>
     </row>
     <row r="128">
@@ -5144,7 +7825,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>ORHANGAZİ</t>
+          <t>ORHANGAZI</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -5154,22 +7835,43 @@
         <v>29.28871669294844</v>
       </c>
       <c r="F128" t="n">
-        <v>15.3764705882353</v>
+        <v>19.5</v>
       </c>
       <c r="G128" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="H128" t="n">
         <v>206.7962080689848</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1195935548820265</v>
+        <v>0.119594</v>
       </c>
       <c r="J128" t="n">
-        <v>978.5294117647059</v>
+        <v>918</v>
       </c>
       <c r="K128" t="n">
         <v>0.5197946416161061</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.517685</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.267998</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.014303</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.28692</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.08232299999999999</v>
       </c>
     </row>
     <row r="129">
@@ -5181,7 +7883,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>TURGUT REİS</t>
+          <t>TURGUT REIS</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -5191,22 +7893,43 @@
         <v>29.2855875284099</v>
       </c>
       <c r="F129" t="n">
-        <v>15.3764705882353</v>
+        <v>6.9</v>
       </c>
       <c r="G129" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="H129" t="n">
         <v>928.6586097534317</v>
       </c>
       <c r="I129" t="n">
-        <v>0.5370581281411343</v>
+        <v>0.537058</v>
       </c>
       <c r="J129" t="n">
-        <v>978.5294117647059</v>
+        <v>742</v>
       </c>
       <c r="K129" t="n">
         <v>0.7170791096986928</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.11254</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.012665</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.288431</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.138397</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.019154</v>
       </c>
     </row>
     <row r="130">
@@ -5218,7 +7941,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>TURGUT REİS</t>
+          <t>TURGUT REIS</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -5228,22 +7951,43 @@
         <v>29.28368776277724</v>
       </c>
       <c r="F130" t="n">
-        <v>15.3764705882353</v>
+        <v>6.9</v>
       </c>
       <c r="G130" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="H130" t="n">
         <v>818.9328501825289</v>
       </c>
       <c r="I130" t="n">
-        <v>0.4736019662910229</v>
+        <v>0.473602</v>
       </c>
       <c r="J130" t="n">
-        <v>978.5294117647059</v>
+        <v>742</v>
       </c>
       <c r="K130" t="n">
         <v>0.7503765644332134</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.11254</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.012665</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.224299</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.138397</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.019154</v>
       </c>
     </row>
     <row r="131">
@@ -5255,7 +7999,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>TURGUT REİS</t>
+          <t>TURGUT REIS</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5265,7 +8009,7 @@
         <v>29.27617532180825</v>
       </c>
       <c r="F131" t="n">
-        <v>15.3764705882353</v>
+        <v>6.9</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -5274,13 +8018,34 @@
         <v>64.34418989938965</v>
       </c>
       <c r="I131" t="n">
-        <v>0.03721127421981153</v>
+        <v>0.037211</v>
       </c>
       <c r="J131" t="n">
-        <v>978.5294117647059</v>
+        <v>742</v>
       </c>
       <c r="K131" t="n">
         <v>0.7202202134730215</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.11254</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.012665</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.001385</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.138397</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.019154</v>
       </c>
     </row>
     <row r="132">
@@ -5292,7 +8057,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>TURGUT REİS</t>
+          <t>TURGUT REIS</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5302,22 +8067,43 @@
         <v>29.28425965041908</v>
       </c>
       <c r="F132" t="n">
-        <v>15.3764705882353</v>
+        <v>6.9</v>
       </c>
       <c r="G132" t="n">
-        <v>0.75</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="H132" t="n">
         <v>686.1171895596593</v>
       </c>
       <c r="I132" t="n">
-        <v>0.3967925453339661</v>
+        <v>0.396793</v>
       </c>
       <c r="J132" t="n">
-        <v>978.5294117647059</v>
+        <v>742</v>
       </c>
       <c r="K132" t="n">
         <v>0.6678608246255248</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.11254</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.012665</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.157444</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.138397</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.019154</v>
       </c>
     </row>
     <row r="133">
@@ -5329,7 +8115,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>TURGUT REİS</t>
+          <t>TURGUT REIS</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5339,22 +8125,43 @@
         <v>29.27966204899259</v>
       </c>
       <c r="F133" t="n">
-        <v>15.3764705882353</v>
+        <v>6.9</v>
       </c>
       <c r="G133" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="H133" t="n">
         <v>291.1615006677863</v>
       </c>
       <c r="I133" t="n">
-        <v>0.1683833530353236</v>
+        <v>0.168383</v>
       </c>
       <c r="J133" t="n">
-        <v>978.5294117647059</v>
+        <v>742</v>
       </c>
       <c r="K133" t="n">
         <v>0.7488221449191328</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.11254</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.012665</v>
+      </c>
+      <c r="N133" t="n">
+        <v>1</v>
+      </c>
+      <c r="O133" t="n">
+        <v>1</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.028353</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.138397</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.019154</v>
       </c>
     </row>
     <row r="134">
@@ -5366,7 +8173,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>TURGUT REİS</t>
+          <t>TURGUT REIS</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5376,7 +8183,7 @@
         <v>29.28478871563883</v>
       </c>
       <c r="F134" t="n">
-        <v>15.3764705882353</v>
+        <v>6.9</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -5385,13 +8192,34 @@
         <v>791.785520080073</v>
       </c>
       <c r="I134" t="n">
-        <v>0.4579022310646134</v>
+        <v>0.457902</v>
       </c>
       <c r="J134" t="n">
-        <v>978.5294117647059</v>
+        <v>742</v>
       </c>
       <c r="K134" t="n">
         <v>0.6922788104925262</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.11254</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.012665</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.209674</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.138397</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.019154</v>
       </c>
     </row>
     <row r="135">
@@ -5403,7 +8231,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>TURGUT REİS</t>
+          <t>TURGUT REIS</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5413,7 +8241,7 @@
         <v>29.28139965617807</v>
       </c>
       <c r="F135" t="n">
-        <v>15.3764705882353</v>
+        <v>6.9</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -5422,13 +8250,34 @@
         <v>580.2279050446639</v>
       </c>
       <c r="I135" t="n">
-        <v>0.3355550783740391</v>
+        <v>0.335555</v>
       </c>
       <c r="J135" t="n">
-        <v>978.5294117647059</v>
+        <v>742</v>
       </c>
       <c r="K135" t="n">
         <v>0.7690736177105905</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.11254</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.012665</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.112597</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.138397</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.019154</v>
       </c>
     </row>
     <row r="136">
@@ -5440,7 +8289,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>YAVUZ SELİM</t>
+          <t>YAVUZ SELIM</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5450,7 +8299,7 @@
         <v>29.27029538524795</v>
       </c>
       <c r="F136" t="n">
-        <v>15.3764705882353</v>
+        <v>17.2</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -5459,13 +8308,34 @@
         <v>574.0454632145472</v>
       </c>
       <c r="I136" t="n">
-        <v>0.3319796733740193</v>
+        <v>0.33198</v>
       </c>
       <c r="J136" t="n">
-        <v>978.5294117647059</v>
+        <v>1146</v>
       </c>
       <c r="K136" t="n">
         <v>0.5654162811568756</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.44373</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.196896</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.110211</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.479325</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.229752</v>
       </c>
     </row>
     <row r="137">
@@ -5477,7 +8347,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>YAVUZ SELİM</t>
+          <t>YAVUZ SELIM</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5487,7 +8357,7 @@
         <v>29.27770833007241</v>
       </c>
       <c r="F137" t="n">
-        <v>15.3764705882353</v>
+        <v>17.2</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -5496,13 +8366,34 @@
         <v>541.3703980748163</v>
       </c>
       <c r="I137" t="n">
-        <v>0.3130831605580849</v>
+        <v>0.313083</v>
       </c>
       <c r="J137" t="n">
-        <v>978.5294117647059</v>
+        <v>1146</v>
       </c>
       <c r="K137" t="n">
         <v>0.6888842131194427</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.44373</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.196896</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.098021</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.479325</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.229752</v>
       </c>
     </row>
     <row r="138">
@@ -5514,7 +8405,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>YAVUZ SELİM</t>
+          <t>YAVUZ SELIM</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5524,22 +8415,43 @@
         <v>29.26663507522861</v>
       </c>
       <c r="F138" t="n">
-        <v>15.3764705882353</v>
+        <v>17.2</v>
       </c>
       <c r="G138" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="H138" t="n">
         <v>761.8791770669751</v>
       </c>
       <c r="I138" t="n">
-        <v>0.4406069145408959</v>
+        <v>0.440607</v>
       </c>
       <c r="J138" t="n">
-        <v>978.5294117647059</v>
+        <v>1146</v>
       </c>
       <c r="K138" t="n">
         <v>0.5722248282517539</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.44373</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.196896</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.194134</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.479325</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.229752</v>
       </c>
     </row>
     <row r="139">
@@ -5551,7 +8463,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>YAVUZ SELİM</t>
+          <t>YAVUZ SELIM</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5561,22 +8473,43 @@
         <v>29.27443788131633</v>
       </c>
       <c r="F139" t="n">
-        <v>15.3764705882353</v>
+        <v>17.2</v>
       </c>
       <c r="G139" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="H139" t="n">
         <v>547.2344772363065</v>
       </c>
       <c r="I139" t="n">
-        <v>0.3164744513345497</v>
+        <v>0.316474</v>
       </c>
       <c r="J139" t="n">
-        <v>978.5294117647059</v>
+        <v>1146</v>
       </c>
       <c r="K139" t="n">
         <v>0.5952844170582819</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.44373</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.196896</v>
+      </c>
+      <c r="N139" t="n">
+        <v>1</v>
+      </c>
+      <c r="O139" t="n">
+        <v>1</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.100156</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.479325</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.229752</v>
       </c>
     </row>
     <row r="140">
@@ -5588,7 +8521,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>YAVUZ SELİM</t>
+          <t>YAVUZ SELIM</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5598,22 +8531,43 @@
         <v>29.27672266261231</v>
       </c>
       <c r="F140" t="n">
-        <v>15.3764705882353</v>
+        <v>17.2</v>
       </c>
       <c r="G140" t="n">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="H140" t="n">
         <v>282.0147939052359</v>
       </c>
       <c r="I140" t="n">
-        <v>0.1630936662107375</v>
+        <v>0.163094</v>
       </c>
       <c r="J140" t="n">
-        <v>978.5294117647059</v>
+        <v>1146</v>
       </c>
       <c r="K140" t="n">
         <v>0.6520633537370493</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.44373</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.196896</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.1225</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.0266</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.479325</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.229752</v>
       </c>
     </row>
     <row r="141">
@@ -5625,7 +8579,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>YAVUZ SELİM</t>
+          <t>YAVUZ SELIM</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5635,10 +8589,10 @@
         <v>29.27704768729355</v>
       </c>
       <c r="F141" t="n">
-        <v>15.3764705882353</v>
+        <v>17.2</v>
       </c>
       <c r="G141" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -5647,10 +8601,31 @@
         <v>0</v>
       </c>
       <c r="J141" t="n">
-        <v>978.5294117647059</v>
+        <v>1146</v>
       </c>
       <c r="K141" t="n">
         <v>0.549844277046868</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.44373</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.196896</v>
+      </c>
+      <c r="N141" t="n">
+        <v>1</v>
+      </c>
+      <c r="O141" t="n">
+        <v>1</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.479325</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.229752</v>
       </c>
     </row>
   </sheetData>
